--- a/naver-place-crawler/results_health/청라_헬스장.xlsx
+++ b/naver-place-crawler/results_health/청라_헬스장.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V21"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="48" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -559,39 +559,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>바디소나타 헬스 PT 청라</t>
+          <t>전칠성의 히어로짐 헬스 PT 그룹PT 청라점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>body_sonata@naver.com</t>
+          <t>whitemurder@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1404-7217</t>
+          <t>0507-1323-9682</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천광역시 서구 중봉대로586번길 15 청연프라자 10층</t>
+          <t>인천 서구 청라커낼로260번길 7-11 퍼스트타워 7층 전칠성의 히어로짐 청라점</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://2080ttt.wixsite.com/bodysonata</t>
+          <t>https://blog.naver.com/whitemurder/224211279556</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -606,13 +606,17 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4vnk5</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1566</v>
+        <v>173</v>
       </c>
       <c r="Q2" t="n">
-        <v>1550</v>
+        <v>495</v>
       </c>
       <c r="R2" t="n">
-        <v>3116</v>
+        <v>668</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,24 +640,24 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>38782467</t>
+          <t>1613152191</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38782467</t>
+          <t>https://m.place.naver.com/place/1613152191</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -675,7 +679,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로 99 지젤엠 A동 4층</t>
+          <t>인천 서구 청라에메랄드로 99 지젤엠 A동 4층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -700,10 +704,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4piz5</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -715,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2802</v>
+        <v>2818</v>
       </c>
       <c r="Q3" t="n">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="R3" t="n">
-        <v>4030</v>
+        <v>4047</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -740,67 +748,71 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>터닝포인트짐 헬스 PT&amp;필라테스 청라점</t>
+          <t>머슬피플 피트니스 헬스 PT 청라</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>tpgym6@naver.com</t>
+          <t>kdkkdk8399@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1340-9221</t>
+          <t>0507-1339-0000</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 서구 중봉대로 594 비전프라자 10층</t>
+          <t>인천 서구 청라한내로72번길 23 701호, 702호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.tpgymcheongna.kr</t>
+          <t>https://blog.naver.com/kdkkdk8399</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4orqz</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -809,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>417</v>
+        <v>370</v>
       </c>
       <c r="Q4" t="n">
-        <v>3431</v>
+        <v>1159</v>
       </c>
       <c r="R4" t="n">
-        <v>3848</v>
+        <v>1529</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +836,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>37450365</t>
+          <t>1197174862</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37450365</t>
+          <t>https://m.place.naver.com/place/1197174862</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -846,34 +858,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>머슬피플 피트니스 헬스 PT 청라</t>
+          <t>바디소나타 헬스 PT 청라</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>kdkkdk8399@naver.com</t>
+          <t>body_sonata@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1339-0000</t>
+          <t>0507-1404-7217</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로72번길 23 701호, 702호</t>
+          <t>인천 서구 중봉대로586번길 15 청연프라자 10층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/kdkkdk8399</t>
+          <t>https://2080ttt.wixsite.com/bodysonata</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -888,13 +900,17 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc46ox</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -903,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>369</v>
+        <v>1578</v>
       </c>
       <c r="Q5" t="n">
-        <v>1125</v>
+        <v>1565</v>
       </c>
       <c r="R5" t="n">
-        <v>1494</v>
+        <v>3143</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +934,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1197174862</t>
+          <t>38782467</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1197174862</t>
+          <t>https://m.place.naver.com/place/38782467</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -940,55 +956,59 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>청라헬스장 킹짐7호점 24시 헬스 PT</t>
+          <t>터닝포인트짐 헬스 PT&amp;필라테스 청라점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>kinggym7@naver.com</t>
+          <t>tpgym6@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1410-9579</t>
+          <t>0507-1340-9221</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 85 C동 지하1층 101호</t>
+          <t>인천 서구 중봉대로 594 비전프라자 10층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/kinggym7</t>
+          <t>https://www.tpgymcheongna.kr</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4o7qi</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -997,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>218</v>
+        <v>416</v>
       </c>
       <c r="Q6" t="n">
-        <v>829</v>
+        <v>3424</v>
       </c>
       <c r="R6" t="n">
-        <v>1047</v>
+        <v>3840</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,51 +1032,51 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2068038054</t>
+          <t>37450365</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2068038054</t>
+          <t>https://m.place.naver.com/place/37450365</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>세인트피트니스 청라점 PT&amp;헬스</t>
+          <t>청라헬스장 킹짐7호점 24시 헬스 PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>soccerkkw2@naver.com</t>
+          <t>kinggym7@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1354-4659</t>
+          <t>0507-1410-9579</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 71 진영메디피아 9층 905호</t>
+          <t>인천 서구 청라라임로 85 C동 지하1층 101호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/soccerkkw2</t>
+          <t>https://blog.naver.com/kinggym7</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1076,10 +1096,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wffw3vu</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1091,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>950</v>
+        <v>220</v>
       </c>
       <c r="Q7" t="n">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="R7" t="n">
-        <v>1873</v>
+        <v>1140</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,61 +1130,61 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1577621981</t>
+          <t>2068038054</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1577621981</t>
+          <t>https://m.place.naver.com/place/2068038054</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>펌퍼스짐 헬스&amp;PT 청라</t>
+          <t>청라PT 바른몸피트니스 2호점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>pumper_gym@naver.com</t>
+          <t>barunmom_fitness@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1476-9054</t>
+          <t>0507-1413-7437</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로 110 파이낸스센터 6층</t>
+          <t>인천 서구 중봉대로612번길 10-22 604, 605호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/pumpers_gym?igsh=MXJueDAwamF5cWpheQ%3D%3D&amp;utm_source=qr</t>
+          <t>https://booking.naver.com/booking/12/bizes/1418130</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1170,10 +1194,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w0qh1pb</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1185,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>256</v>
+        <v>77</v>
       </c>
       <c r="Q8" t="n">
-        <v>237</v>
+        <v>212</v>
       </c>
       <c r="R8" t="n">
-        <v>493</v>
+        <v>289</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,61 +1228,61 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1828279952</t>
+          <t>2032271782</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1828279952</t>
+          <t>https://m.place.naver.com/place/2032271782</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>좋은습관 PT STUDIO 청라</t>
+          <t>청라PT 바른몸피트니스 1호점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>goodhabit_ch@naver.com</t>
+          <t>barunmom_fitness@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1435-9902</t>
+          <t>0507-1340-7437</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로72번길 7-15 센트럴시티 2층 청라PT 좋은습관</t>
+          <t>인천 서구 청라루비로 93 루비타워 4층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/goodhabit_ch</t>
+          <t>https://booking.naver.com/booking/12/bizes/815141</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1264,10 +1292,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w469g7</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1279,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>540</v>
+        <v>300</v>
       </c>
       <c r="Q9" t="n">
-        <v>258</v>
+        <v>667</v>
       </c>
       <c r="R9" t="n">
-        <v>798</v>
+        <v>967</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,51 +1326,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1404702049</t>
+          <t>1059514904</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1404702049</t>
+          <t>https://m.place.naver.com/place/1059514904</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>하루50분 PT필라테스 청라4호점</t>
+          <t>웰무브 근골격운동센터 청라점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>rladnwjd802@naver.com</t>
+          <t>wellmove_ex@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1423-7258</t>
+          <t>0507-1423-9397</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로 78 4층 405호</t>
+          <t>인천 서구 청라라임로 71 8층 808호, 809호 웰무브 근골격운동센터</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/rladnwjd802</t>
+          <t>https://www.instagram.com/wellmove_1</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1353,15 +1385,19 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5w2i3</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1369,17 +1405,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>122</v>
+        <v>51</v>
       </c>
       <c r="Q10" t="n">
-        <v>113</v>
+        <v>143</v>
       </c>
       <c r="R10" t="n">
-        <v>235</v>
+        <v>194</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,47 +1424,51 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2038838362</t>
+          <t>1594642239</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2038838362</t>
+          <t>https://m.place.naver.com/place/1594642239</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>마스터 와이짐 PT 청라점</t>
+          <t>강자존 리햅 1대1 PT샵 루원시티점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>master_y_gym@naver.com</t>
+          <t>tjdwnsldlek@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1365-0715</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로288번길 10 더스페이스타워 305호</t>
+          <t>인천 서구 봉오재3로 116 3층 306호 강자존 리햅 1대1 PT샵 루원시티점</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/master__y_gym</t>
+          <t>https://blog.naver.com/tjdwnsldlek/224143719751</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1443,15 +1483,19 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wwi3sps</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1459,17 +1503,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>356</v>
+        <v>95</v>
       </c>
       <c r="Q11" t="n">
-        <v>525</v>
+        <v>68</v>
       </c>
       <c r="R11" t="n">
-        <v>881</v>
+        <v>163</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1478,51 +1522,51 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1200262369</t>
+          <t>2001611714</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1200262369</t>
+          <t>https://m.place.naver.com/place/2001611714</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>커넥트바디 재활&amp;PT 청라점</t>
+          <t>키필라테스 청라점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>connect-body@naver.com</t>
+          <t>keypilates@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1380-8515</t>
+          <t>1555-7745</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>인천광역시 서구 보석로12번안길 35 1층</t>
+          <t>인천 서구 청라커낼로288번길 10 4층 408호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/connect-body/223458723996</t>
+          <t>https://www.instagram.com/keypilates.kr</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1537,15 +1581,19 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wyozl7z</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
           <t>X</t>
@@ -1557,13 +1605,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>154</v>
+        <v>15</v>
       </c>
       <c r="Q12" t="n">
-        <v>447</v>
+        <v>19</v>
       </c>
       <c r="R12" t="n">
-        <v>601</v>
+        <v>34</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1572,859 +1620,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1346258755</t>
+          <t>2074412271</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1346258755</t>
+          <t>https://m.place.naver.com/place/2074412271</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>청라PT 바른몸피트니스 1호점</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>barunmom_fitness@naver.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0507-1340-7437</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>인천광역시 서구 청라루비로 93 루비타워 4층</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://booking.naver.com/booking/12/bizes/815141</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>297</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>603</v>
-      </c>
-      <c r="R13" t="n">
-        <v>900</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>1059514904</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1059514904</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>사이언스핏 PT필라 청라점</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>sciencefit@naver.com</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0507-1487-2044</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>인천광역시 서구 중봉대로612번길 10-8 반안프라자 401호, 402호, 403호</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/science_fit__</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>104</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>774</v>
-      </c>
-      <c r="R14" t="n">
-        <v>878</v>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>1329193780</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1329193780</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>젠틀레이디짐 PT&amp;필라테스</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>gentlelady_gym@naver.com</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0507-1384-8303</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>인천광역시 서구 청라커낼로288번길 26 상가동 103동 324호</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/gentlelady_gym</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P15" t="n">
-        <v>532</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>612</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1144</v>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>1188954884</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1188954884</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>슬릭부스트 루원시티점</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>sleekboost__lu1@naver.com</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0507-1390-4983</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>인천광역시 서구 새오개로111번안길 26 3층</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/sleekboost_lu1/</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P16" t="n">
-        <v>310</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>235</v>
-      </c>
-      <c r="R16" t="n">
-        <v>545</v>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>1634343801</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1634343801</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>여성전용 아이리스짐&amp;필라테스</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>irisgym@naver.com</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0507-1356-0413</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>인천광역시 서구 청라에메랄드로102번길 8-26 301호</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>https://smartstore.naver.com/</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P17" t="n">
-        <v>175</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>319</v>
-      </c>
-      <c r="R17" t="n">
-        <v>494</v>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>1553359701</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1553359701</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>고다짐 청라점</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>cjdfk2402@naver.com</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>032-565-5466</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>인천광역시 서구 청라에메랄드로 134 상가동 지1층 비103호</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>https://www.godagym.com</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P18" t="n">
-        <v>132</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>467</v>
-      </c>
-      <c r="R18" t="n">
-        <v>599</v>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>1295044192</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1295044192</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>팬텀짐 루원시티점</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>phantomgym_lu1@naver.com</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>0507-1331-0050</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>인천광역시 서구 새오개로111번안길 19-1 유성프라자 401, 402, 403호</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/phantomgym_lu1</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P19" t="n">
-        <v>760</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>457</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1217</v>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>1088258551</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1088258551</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>청년피티 청라점</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>cnpt3455@naver.com</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>0507-1434-3455</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>인천광역시 서구 중봉대로 610 3층</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>https://cnptoffical.qshop.ai/</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P20" t="n">
-        <v>422</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>232</v>
-      </c>
-      <c r="R20" t="n">
-        <v>654</v>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>1293398871</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1293398871</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>F45 청라</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>f45cheongna@naver.com</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>인천광역시 서구 청라루비로 76 2층 F45 청라</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/f45cheongna</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P21" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>27</v>
-      </c>
-      <c r="R21" t="n">
-        <v>29</v>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>2038283950</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/2038283950</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/청라_헬스장.xlsx
+++ b/naver-place-crawler/results_health/청라_헬스장.xlsx
@@ -417,11 +417,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>전칠성의 히어로짐 헬스 PT 그룹PT 청라점</t>
+          <t>청라스포츠센터 헬스 PT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>whitemurder@naver.com</t>
+          <t>uzwuzw@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1323-9682</t>
+          <t>0507-1300-4100</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천 서구 청라커낼로260번길 7-11 퍼스트타워 7층 전칠성의 히어로짐 청라점</t>
+          <t>인천 서구 청라에메랄드로 99 지젤엠 A동 4층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/whitemurder/224211279556</t>
+          <t>https://www.instagram.com/csc_training_center</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4vnk5</t>
+          <t>https://talk.naver.com/ct/w4piz5</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>173</v>
+        <v>2827</v>
       </c>
       <c r="Q2" t="n">
-        <v>495</v>
+        <v>1229</v>
       </c>
       <c r="R2" t="n">
-        <v>668</v>
+        <v>4056</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,17 +640,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1613152191</t>
+          <t>1213983093</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1613152191</t>
+          <t>https://m.place.naver.com/place/1213983093</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -662,29 +662,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>청라스포츠센터 헬스 PT</t>
+          <t>머슬피플 피트니스 헬스 PT 청라</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>uzwuzw@naver.com</t>
+          <t>kdkkdk8399@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1300-4100</t>
+          <t>0507-1339-0000</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천 서구 청라에메랄드로 99 지젤엠 A동 4층</t>
+          <t>인천 서구 청라한내로72번길 23 701호, 702호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/csc_training_center</t>
+          <t>https://blog.naver.com/kdkkdk8399</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4piz5</t>
+          <t>https://talk.naver.com/ct/w4orqz</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2818</v>
+        <v>370</v>
       </c>
       <c r="Q3" t="n">
-        <v>1229</v>
+        <v>1160</v>
       </c>
       <c r="R3" t="n">
-        <v>4047</v>
+        <v>1530</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,51 +738,51 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1213983093</t>
+          <t>1197174862</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1213983093</t>
+          <t>https://m.place.naver.com/place/1197174862</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>머슬피플 피트니스 헬스 PT 청라</t>
+          <t>바디소나타 헬스 PT 청라</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>kdkkdk8399@naver.com</t>
+          <t>body_sonata@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1339-0000</t>
+          <t>0507-1404-7217</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천 서구 청라한내로72번길 23 701호, 702호</t>
+          <t>인천 서구 중봉대로586번길 15 청연프라자 10층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/kdkkdk8399</t>
+          <t>https://2080ttt.wixsite.com/bodysonata</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4orqz</t>
+          <t>https://talk.naver.com/ct/wc46ox</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>370</v>
+        <v>1578</v>
       </c>
       <c r="Q4" t="n">
-        <v>1159</v>
+        <v>1571</v>
       </c>
       <c r="R4" t="n">
-        <v>1529</v>
+        <v>3149</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,17 +836,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1197174862</t>
+          <t>38782467</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1197174862</t>
+          <t>https://m.place.naver.com/place/38782467</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -858,29 +858,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>바디소나타 헬스 PT 청라</t>
+          <t>터닝포인트짐 헬스 PT&amp;필라테스 청라점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>body_sonata@naver.com</t>
+          <t>tpgym6@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1404-7217</t>
+          <t>0507-1340-9221</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천 서구 중봉대로586번길 15 청연프라자 10층</t>
+          <t>인천 서구 중봉대로 594 비전프라자 10층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://2080ttt.wixsite.com/bodysonata</t>
+          <t>https://www.tpgymcheongna.kr</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wc46ox</t>
+          <t>https://talk.naver.com/ct/w4o7qi</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1578</v>
+        <v>417</v>
       </c>
       <c r="Q5" t="n">
-        <v>1565</v>
+        <v>3424</v>
       </c>
       <c r="R5" t="n">
-        <v>3143</v>
+        <v>3841</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,66 +934,66 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>38782467</t>
+          <t>37450365</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38782467</t>
+          <t>https://m.place.naver.com/place/37450365</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>터닝포인트짐 헬스 PT&amp;필라테스 청라점</t>
+          <t>청라헬스장 킹짐7호점 24시 헬스 PT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>tpgym6@naver.com</t>
+          <t>kinggym7@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1340-9221</t>
+          <t>0507-1410-9579</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천 서구 중봉대로 594 비전프라자 10층</t>
+          <t>인천 서구 청라라임로 85 C동 지하1층 101호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.tpgymcheongna.kr</t>
+          <t>https://blog.naver.com/kinggym7</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1003,12 +1003,12 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4o7qi</t>
+          <t>https://talk.naver.com/ct/wffw3vu</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>416</v>
+        <v>220</v>
       </c>
       <c r="Q6" t="n">
-        <v>3424</v>
+        <v>926</v>
       </c>
       <c r="R6" t="n">
-        <v>3840</v>
+        <v>1146</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>37450365</t>
+          <t>2068038054</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37450365</t>
+          <t>https://m.place.naver.com/place/2068038054</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1054,29 +1054,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>청라헬스장 킹짐7호점 24시 헬스 PT</t>
+          <t>AMG피트니스 석남점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>kinggym7@naver.com</t>
+          <t>amg5565@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1410-9579</t>
+          <t>032-572-6800</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천 서구 청라라임로 85 C동 지하1층 101호</t>
+          <t>인천 서구 길주로 79 성한캐슬 11층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/kinggym7</t>
+          <t>https://blog.naver.com/amg5565</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wffw3vu</t>
+          <t>https://talk.naver.com/ct/wcfgp2</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1115,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>220</v>
+        <v>501</v>
       </c>
       <c r="Q7" t="n">
-        <v>920</v>
+        <v>613</v>
       </c>
       <c r="R7" t="n">
-        <v>1140</v>
+        <v>1114</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,17 +1130,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2068038054</t>
+          <t>1409341657</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2068038054</t>
+          <t>https://m.place.naver.com/place/1409341657</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q8" t="n">
         <v>212</v>
       </c>
       <c r="R8" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1314,10 +1314,10 @@
         <v>300</v>
       </c>
       <c r="Q9" t="n">
-        <v>667</v>
+        <v>679</v>
       </c>
       <c r="R9" t="n">
-        <v>967</v>
+        <v>979</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1507,10 +1507,10 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Q11" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="R11" t="n">
         <v>163</v>
@@ -1532,105 +1532,203 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>키필라테스 청라점</t>
+          <t>좋은습관 PT STUDIO 청라</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>keypilates@naver.com</t>
+          <t>goodhabit_ch@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1555-7745</t>
+          <t>0507-1435-9902</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
+          <t>인천 서구 청라한내로72번길 7-15 센트럴시티 2층 청라PT 좋은습관</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/goodhabit_ch</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w46ocb</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>546</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>259</v>
+      </c>
+      <c r="R12" t="n">
+        <v>805</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1404702049</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1404702049</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>키필라테스 청라점</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>keypilates@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1555-7745</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
           <t>인천 서구 청라커낼로288번길 10 4층 408호</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>https://www.instagram.com/keypilates.kr</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
         <is>
           <t>https://talk.naver.com/ct/wyozl7z</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
         <v>15</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="Q13" t="n">
         <v>19</v>
       </c>
-      <c r="R12" t="n">
+      <c r="R13" t="n">
         <v>34</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
         <is>
           <t>2074412271</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/2074412271</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/청라_헬스장.xlsx
+++ b/naver-place-crawler/results_health/청라_헬스장.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -824,10 +824,10 @@
         <v>1578</v>
       </c>
       <c r="Q4" t="n">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="R4" t="n">
-        <v>3149</v>
+        <v>3150</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -1020,10 +1020,10 @@
         <v>220</v>
       </c>
       <c r="Q6" t="n">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="R6" t="n">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1314,10 +1314,10 @@
         <v>300</v>
       </c>
       <c r="Q9" t="n">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="R9" t="n">
-        <v>979</v>
+        <v>982</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1412,10 +1412,10 @@
         <v>51</v>
       </c>
       <c r="Q10" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R10" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1539,34 +1539,34 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>좋은습관 PT STUDIO 청라</t>
+          <t>키필라테스 청라점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>goodhabit_ch@naver.com</t>
+          <t>keypilates@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1435-9902</t>
+          <t>1555-7745</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>인천 서구 청라한내로72번길 7-15 센트럴시티 2층 청라PT 좋은습관</t>
+          <t>인천 서구 청라커낼로288번길 10 4층 408호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/goodhabit_ch</t>
+          <t>https://www.instagram.com/keypilates.kr</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w46ocb</t>
+          <t>https://talk.naver.com/ct/wyozl7z</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1605,13 +1605,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>546</v>
+        <v>15</v>
       </c>
       <c r="Q12" t="n">
-        <v>259</v>
+        <v>19</v>
       </c>
       <c r="R12" t="n">
-        <v>805</v>
+        <v>34</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1620,113 +1620,15 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1404702049</t>
+          <t>2074412271</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1404702049</t>
+          <t>https://m.place.naver.com/place/2074412271</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>필라테스</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>키필라테스 청라점</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>keypilates@naver.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>1555-7745</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>인천 서구 청라커낼로288번길 10 4층 408호</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/keypilates.kr</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wyozl7z</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>19</v>
-      </c>
-      <c r="R13" t="n">
-        <v>34</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>2074412271</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/2074412271</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/청라_헬스장.xlsx
+++ b/naver-place-crawler/results_health/청라_헬스장.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="49" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>청라스포츠센터 헬스 PT</t>
+          <t>핏박스 PT&amp;그룹PT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>uzwuzw@naver.com</t>
+          <t>master_ssim@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1300-4100</t>
+          <t>0507-1370-8932</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천 서구 청라에메랄드로 99 지젤엠 A동 4층</t>
+          <t>인천광역시 서구 중봉대로 588 9층 핏박스PT</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/csc_training_center</t>
+          <t>https://blog.naver.com/master_ssim</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,19 +601,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4piz5</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -625,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2827</v>
+        <v>120</v>
       </c>
       <c r="Q2" t="n">
-        <v>1229</v>
+        <v>456</v>
       </c>
       <c r="R2" t="n">
-        <v>4056</v>
+        <v>576</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1213983093</t>
+          <t>1839479269</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1213983093</t>
+          <t>https://m.place.naver.com/place/1839479269</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -662,29 +658,25 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>머슬피플 피트니스 헬스 PT 청라</t>
+          <t>청라웰카운티스포츠센터</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>kdkkdk8399@naver.com</t>
+          <t>newstation@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0507-1339-0000</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천 서구 청라한내로72번길 23 701호, 702호</t>
+          <t>인천광역시 서구 청라에메랄드로 156</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/kdkkdk8399</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -694,24 +686,20 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4orqz</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -719,17 +707,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>370</v>
+        <v>27</v>
       </c>
       <c r="Q3" t="n">
-        <v>1160</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1530</v>
+        <v>27</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,12 +726,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1197174862</t>
+          <t>1074312806</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1197174862</t>
+          <t>https://m.place.naver.com/place/1074312806</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -755,34 +743,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>바디소나타 헬스 PT 청라</t>
+          <t>포텐휘트니스 헬스&amp;PT 루원시티점 24시</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>body_sonata@naver.com</t>
+          <t>eohgdt4618@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1404-7217</t>
+          <t>0507-1454-0823</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천 서구 중봉대로586번길 15 청연프라자 10층</t>
+          <t>인천광역시 서구 봉오재3로 111 정석빌딩 4, 5층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://2080ttt.wixsite.com/bodysonata</t>
+          <t>https://blog.naver.com/eohgdt4618</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -802,14 +790,10 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wc46ox</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -821,13 +805,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1578</v>
+        <v>201</v>
       </c>
       <c r="Q4" t="n">
-        <v>1572</v>
+        <v>739</v>
       </c>
       <c r="R4" t="n">
-        <v>3150</v>
+        <v>940</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,12 +820,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>38782467</t>
+          <t>1191364163</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38782467</t>
+          <t>https://m.place.naver.com/place/1191364163</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -853,44 +837,44 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>터닝포인트짐 헬스 PT&amp;필라테스 청라점</t>
+          <t>고다짐 청라점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>tpgym6@naver.com</t>
+          <t>cjdfk2402@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1340-9221</t>
+          <t>032-565-5466</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천 서구 중봉대로 594 비전프라자 10층</t>
+          <t>인천광역시 서구 청라에메랄드로 134 상가동 지1층 비103호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.tpgymcheongna.kr</t>
+          <t>https://www.godagym.com</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -900,14 +884,10 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4o7qi</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>O</t>
@@ -919,13 +899,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>417</v>
+        <v>132</v>
       </c>
       <c r="Q5" t="n">
-        <v>3424</v>
+        <v>455</v>
       </c>
       <c r="R5" t="n">
-        <v>3841</v>
+        <v>587</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,12 +914,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>37450365</t>
+          <t>1295044192</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37450365</t>
+          <t>https://m.place.naver.com/place/1295044192</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -956,29 +936,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>청라헬스장 킹짐7호점 24시 헬스 PT</t>
+          <t>스밀로짐 헬스 PT 청라</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>kinggym7@naver.com</t>
+          <t>smilogym@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1410-9579</t>
+          <t>0507-1360-1516</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천 서구 청라라임로 85 C동 지하1층 101호</t>
+          <t>인천광역시 서구 청라커낼로260번길 7-19 6층 스밀로짐</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/kinggym7</t>
+          <t>https://smartstore.naver.com/smilogym</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -993,19 +973,15 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wffw3vu</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1017,13 +993,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>220</v>
+        <v>87</v>
       </c>
       <c r="Q6" t="n">
-        <v>927</v>
+        <v>46</v>
       </c>
       <c r="R6" t="n">
-        <v>1147</v>
+        <v>133</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,12 +1008,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2068038054</t>
+          <t>1711058369</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2068038054</t>
+          <t>https://m.place.naver.com/place/1711058369</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1054,29 +1030,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AMG피트니스 석남점</t>
+          <t>아놀드홍짐 청라점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>amg5565@naver.com</t>
+          <t>hanki1213@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>032-572-6800</t>
+          <t>032-567-8296</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천 서구 길주로 79 성한캐슬 11층</t>
+          <t>인천광역시 서구 중봉대로 587 홈플러스6층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/amg5565</t>
+          <t>https://blog.naver.com/hanki1213</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1096,14 +1072,10 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wcfgp2</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1111,17 +1083,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>501</v>
+        <v>3</v>
       </c>
       <c r="Q7" t="n">
-        <v>613</v>
+        <v>281</v>
       </c>
       <c r="R7" t="n">
-        <v>1114</v>
+        <v>284</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,12 +1102,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1409341657</t>
+          <t>37288445</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1409341657</t>
+          <t>https://m.place.naver.com/place/37288445</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1147,61 +1119,57 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>청라PT 바른몸피트니스 2호점</t>
+          <t>제로짐 재활운동연구소 청라</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>barunmom_fitness@naver.com</t>
+          <t>zero_gym00@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1413-7437</t>
+          <t>0507-1493-3498</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천 서구 중봉대로612번길 10-22 604, 605호</t>
+          <t>인천광역시 서구 중봉대로586번길 9-19 2층 청라 제로짐</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/12/bizes/1418130</t>
+          <t>https://blog.naver.com/zero_gym00</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w0qh1pb</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1213,13 +1181,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="Q8" t="n">
-        <v>212</v>
+        <v>415</v>
       </c>
       <c r="R8" t="n">
-        <v>290</v>
+        <v>499</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,12 +1196,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2032271782</t>
+          <t>1735402390</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2032271782</t>
+          <t>https://m.place.naver.com/place/1735402390</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1245,61 +1213,57 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>청라PT 바른몸피트니스 1호점</t>
+          <t>크로스핏 굿데이</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>barunmom_fitness@naver.com</t>
+          <t>hooksuksuk@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1340-7437</t>
+          <t>0507-1470-7606</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천 서구 청라루비로 93 루비타워 4층</t>
+          <t>인천광역시 서구 승학로 223 지하1층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/12/bizes/815141</t>
+          <t>https://www.instagram.com/crossfit_goodday</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w469g7</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1311,13 +1275,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>682</v>
+        <v>7</v>
       </c>
       <c r="R9" t="n">
-        <v>982</v>
+        <v>7</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,12 +1290,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1059514904</t>
+          <t>1117551454</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1059514904</t>
+          <t>https://m.place.naver.com/place/1117551454</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1343,39 +1307,39 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>웰무브 근골격운동센터 청라점</t>
+          <t>카우짐24시 서구청역점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>wellmove_ex@naver.com</t>
+          <t>coco951215@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1423-9397</t>
+          <t>0507-1376-7926</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천 서구 청라라임로 71 8층 808호, 809호 웰무브 근골격운동센터</t>
+          <t>인천광역시 서구 탁옥로51번길 11 702호, 703호, 704호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/wellmove_1</t>
+          <t>https://link.inpock.co.kr/cowgymseogu</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1385,19 +1349,15 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5w2i3</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1405,17 +1365,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>51</v>
+        <v>1021</v>
       </c>
       <c r="Q10" t="n">
-        <v>144</v>
+        <v>324</v>
       </c>
       <c r="R10" t="n">
-        <v>195</v>
+        <v>1345</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1424,12 +1384,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1594642239</t>
+          <t>1106839652</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1594642239</t>
+          <t>https://m.place.naver.com/place/1106839652</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1446,29 +1406,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>강자존 리햅 1대1 PT샵 루원시티점</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>tjdwnsldlek@naver.com</t>
-        </is>
-      </c>
+          <t>피지컬뷰티짐 청라점 PT &amp; 헬스</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1365-0715</t>
+          <t>0507-1358-0655</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천 서구 봉오재3로 116 3층 306호 강자존 리햅 1대1 PT샵 루원시티점</t>
+          <t>인천광역시 서구 청라커낼로 270 2층 피지컬뷰티짐 청라점</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/tjdwnsldlek/224143719751</t>
+          <t>https://www.youtube.com/c/피지컬뷰티</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1488,14 +1444,10 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wwi3sps</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1503,17 +1455,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="Q11" t="n">
-        <v>69</v>
+        <v>511</v>
       </c>
       <c r="R11" t="n">
-        <v>163</v>
+        <v>599</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1522,12 +1474,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2001611714</t>
+          <t>1693588410</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2001611714</t>
+          <t>https://m.place.naver.com/place/1693588410</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1539,34 +1491,34 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>키필라테스 청라점</t>
+          <t>청라헬스장 킹짐7호점 24시 헬스 PT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>keypilates@naver.com</t>
+          <t>kinggym7@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1555-7745</t>
+          <t>0507-1410-9579</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>인천 서구 청라커낼로288번길 10 4층 408호</t>
+          <t>인천광역시 서구 청라라임로 85 C동 지하1층 101호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/keypilates.kr</t>
+          <t>https://blog.naver.com/kinggym7</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1581,19 +1533,15 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wyozl7z</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>X</t>
@@ -1605,13 +1553,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>15</v>
+        <v>220</v>
       </c>
       <c r="Q12" t="n">
-        <v>19</v>
+        <v>927</v>
       </c>
       <c r="R12" t="n">
-        <v>34</v>
+        <v>1147</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1620,15 +1568,6003 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2074412271</t>
+          <t>2068038054</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2074412271</t>
+          <t>https://m.place.naver.com/place/2068038054</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>트리니티 피트니스 헬스 PT 청라</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>trinity_fit@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 크리스탈로 84 청라 레이크가든 빌딩 5층</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/trinity_fit/</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>919</v>
+      </c>
+      <c r="R13" t="n">
+        <v>999</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1044334882</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1044334882</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>와이짐휘트니스</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>moonseok84@naver.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0507-1364-9607</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라커낼로260번길 11 4층 401호</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/moonseok84</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>94</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>166</v>
+      </c>
+      <c r="R14" t="n">
+        <v>260</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>1999952799</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1999952799</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>에이에이헬스 PT&amp;필라테스재활 청라점</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>somin7369@naver.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0507-1340-8864</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라커낼로260번길 27 스타벅스 청라 한신점 오른편 지하1층</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>195</v>
+      </c>
+      <c r="R15" t="n">
+        <v>195</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>2076358875</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2076358875</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>크로스핏 A4U</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>kwlcl707@naver.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0507-1352-7329</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 담지로86번길 16-36 1층 A4U CROSSFIT</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/crossfit_a4u</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>88</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>101</v>
+      </c>
+      <c r="R16" t="n">
+        <v>189</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>1104364395</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1104364395</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>센스짐 석남점</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>sensegym_jjy@naver.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 가정로 308 석남프라자 B1층</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://litt.ly/sensegym_jjy</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>1293</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>617</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1910</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1507969525</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1507969525</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>청라스포츠센터 헬스 PT</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>uzwuzw@naver.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0507-1300-4100</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라에메랄드로 99 지젤엠 A동 4층</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/csc_training_center</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>2827</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1229</v>
+      </c>
+      <c r="R18" t="n">
+        <v>4056</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>1213983093</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1213983093</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>엔알 휘트니스 경서점</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>hayth1212@naver.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0507-1367-7749</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 도요지로 24 2층</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/hayth1212</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>177</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>295</v>
+      </c>
+      <c r="R19" t="n">
+        <v>472</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>37373516</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37373516</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>머슬피플 피트니스 헬스 PT 청라</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>kdkkdk8399@naver.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0507-1339-0000</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라한내로72번길 23 701호, 702호</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/kdkkdk8399</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>370</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1161</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1531</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1197174862</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1197174862</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>바른피티샵</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>kyh880903@naver.com</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0507-1354-3897</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 중봉대로612번길 10-22 2층</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/kyh880903</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>142</v>
+      </c>
+      <c r="R21" t="n">
+        <v>242</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>1845302007</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1845302007</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>크로스핏 청라</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>kwlcl707@naver.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0507-1337-5001</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 보석로 4 1층</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>http://cafe.naver.com/crossfitcheongna</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>603</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>68</v>
+      </c>
+      <c r="R22" t="n">
+        <v>671</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>1600815804</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1600815804</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>어라운드 헬스&amp;PT 청라</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>aroundgym_1@naver.com</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0507-1327-9593</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 중봉대로586번길 9-4 3층 307호 어라운드 헬스&amp;PT</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/aroundgym_1</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>392</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>286</v>
+      </c>
+      <c r="R23" t="n">
+        <v>678</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>1698654705</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1698654705</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>프리짐 청라점</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>freegym24@naver.com</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0507-1397-6779</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라한내로72번길 17 3층 307~312호</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/freegym24</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>103</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>103</v>
+      </c>
+      <c r="R24" t="n">
+        <v>206</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>1241238840</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1241238840</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>록 피트니스 R.O.K 헬스&amp;PT 가정점</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>rok03903@naver.com</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 염곡로464번길 23 엔시티타워 7층</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/rok03903</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>723</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1172</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1895</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>1475425565</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1475425565</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>크롬 트레이닝 스튜디오</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>chrome2026@naver.com</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0507-1314-3439</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 봉오재3로94번길 11 mk타워 3층 308, 309호</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/chrome2026</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>3</v>
+      </c>
+      <c r="R26" t="n">
+        <v>3</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>2002611415</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2002611415</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>세인트피트니스 청라점 PT&amp;헬스</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>soccerkkw2@naver.com</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0507-1354-4659</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라라임로 71 진영메디피아 9층 905호</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/soccerkkw2</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>948</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>916</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1864</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>1577621981</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1577621981</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>크로스핏 피포피 가정점</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>bow14674@naver.com</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0507-1345-3994</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 새오개로111번안길 19-1 지하 1층</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/bow14674</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>84</v>
+      </c>
+      <c r="R28" t="n">
+        <v>139</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>1971300109</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1971300109</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>레인헬스PT 서구청점</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>sonyeopps@naver.com</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0507-1487-0787</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 탁옥로 37 2층 201호</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/sonyeopps</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>124</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>166</v>
+      </c>
+      <c r="R29" t="n">
+        <v>290</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>1799609656</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1799609656</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>펌퍼스짐 헬스&amp;PT 청라</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>pumper_gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0507-1476-9054</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라한내로 110 파이낸스센터 6층</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/pumpers_gym?igsh=MXJueDAwamF5cWpheQ%3D%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>256</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>252</v>
+      </c>
+      <c r="R30" t="n">
+        <v>508</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>1828279952</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1828279952</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>바디소나타 헬스 PT 청라</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>body_sonata@naver.com</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0507-1404-7217</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 중봉대로586번길 15 청연프라자 10층</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://2080ttt.wixsite.com/bodysonata</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>1578</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1573</v>
+      </c>
+      <c r="R31" t="n">
+        <v>3151</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>38782467</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38782467</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>하운드짐</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>houndgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0507-1313-9986</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 솔빛로28번길 12 리마프라자 2층</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/houndgym</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>101</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>149</v>
+      </c>
+      <c r="R32" t="n">
+        <v>250</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>1606787218</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1606787218</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>청라 피트니스비에이 PT&amp;헬스</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>fitnessba@naver.com</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0507-1359-0563</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 푸른로16번길 15 1층</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/fitnessba</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>61</v>
+      </c>
+      <c r="R33" t="n">
+        <v>90</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>1922697320</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1922697320</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>F45 청라</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>f45cheongna@naver.com</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라루비로 76 2층 F45 청라</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/f45cheongna</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>30</v>
+      </c>
+      <c r="R34" t="n">
+        <v>32</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>2038283950</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2038283950</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>청년피티 청라점</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>cnpt3455@naver.com</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0507-1434-3455</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 중봉대로 610 3층</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://cnptoffical.qshop.ai/</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>433</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>235</v>
+      </c>
+      <c r="R35" t="n">
+        <v>668</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>1293398871</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1293398871</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>전칠성의 히어로짐 헬스 PT 그룹PT 청라점</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>whitemurder@naver.com</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0507-1323-9682</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라커낼로260번길 7-11 퍼스트타워 7층 전칠성의 히어로짐 청라점</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/whitemurder/224211279556</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>173</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>495</v>
+      </c>
+      <c r="R36" t="n">
+        <v>668</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>1613152191</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1613152191</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>해시피트니스 청라점</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>hashfit@naver.com</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0507-1492-3101</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라한내로 96 하엘에스페이스12층</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hashfit_ness/</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>533</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>735</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1268</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>1799409304</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1799409304</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>휘트니트센터</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>rnltls5612@naver.com</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라커낼로 232</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>5</v>
+      </c>
+      <c r="R38" t="n">
+        <v>10</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>85758557</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/85758557</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>행복 휘트니스</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>maengdrive_@naver.com</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0507-1376-3581</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 새오개로54번길 15-1 3층</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/_shinseok_/</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>6</v>
+      </c>
+      <c r="R39" t="n">
+        <v>12</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>1455766468</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1455766468</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>팬텀짐 루원시티점</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>phantomgym_lu1@naver.com</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0507-1331-0050</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 새오개로111번안길 19-1 유성프라자 401, 402, 403호</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/phantomgym_lu1</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>757</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>457</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1214</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>1088258551</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1088258551</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>올나잇 피트니스 가정점 헬스&amp;PT</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>rdx329@naver.com</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0507-1475-6636</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 가정로 451 벨라미센텀시티2차 13층 1320호</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/all.night_3</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>1743</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>536</v>
+      </c>
+      <c r="R41" t="n">
+        <v>2279</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>1898172914</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1898172914</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>피지컬뷰티짐 신현점</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>physicalbeauty@naver.com</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0507-1302-0654</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 가정로 369 4층 401호</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/c/피지컬뷰티</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>375</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1103</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1478</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>1383014310</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1383014310</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>터닝포인트짐 헬스 PT&amp;필라테스 청라점</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>tpgym6@naver.com</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0507-1340-9221</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 중봉대로 594 비전프라자 10층</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://www.tpgymcheongna.kr</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>417</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>3424</v>
+      </c>
+      <c r="R43" t="n">
+        <v>3841</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>37450365</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37450365</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>여성전용 아이리스짐&amp;필라테스</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>irisgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0507-1356-0413</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라에메랄드로102번길 8-26 301호</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>175</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>321</v>
+      </c>
+      <c r="R44" t="n">
+        <v>496</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>1553359701</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1553359701</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>엘티시앤짐</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0507-1431-5227</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라한내로 96 8층 802호</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>2</v>
+      </c>
+      <c r="R45" t="n">
+        <v>2</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>2002395008</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2002395008</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>터닝포인트짐 헬스&amp;PT 신현점</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>turning1210@naver.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0507-1368-9220</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 가정로 375 5층 터닝포인트짐 신현점</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/turning1210</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>956</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>1939</v>
+      </c>
+      <c r="R46" t="n">
+        <v>2895</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>37452550</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37452550</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>엑스짐 신현점</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>xgym01@naver.com</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0507-1402-2033</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 가정로 419 . 4층 401호, 402호(신현동)</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/x_gym_can?igsh=NGxodHQ0b2FlbWFr</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>120</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>430</v>
+      </c>
+      <c r="R47" t="n">
+        <v>550</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>1413141073</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1413141073</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>마이짐 PT 청라점</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>better__life@naver.com</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0507-1378-3868</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 중봉대로612번길 10-20 6층 마이짐</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mygym_pt_official?igsh=dGMxNWw2eG40MWtx</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>57</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>396</v>
+      </c>
+      <c r="R48" t="n">
+        <v>453</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>1099553298</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1099553298</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>엘핏 청라점</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>lemongym-cn@naver.com</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0507-1428-5104</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 옥빛로13번길 3 1층 엘핏</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/lemongym-cn</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>89</v>
+      </c>
+      <c r="R49" t="n">
+        <v>154</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>1196898702</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1196898702</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>하루50분 PT필라테스 가정5호점</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>rladnwjd802@naver.com</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0507-1309-6293</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 염곡로498번안길 18 이규프라자 3층</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>http://www.haru50.com</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>2084849885</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2084849885</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>청라PT 바른몸피트니스 1호점</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>barunmom_fitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0507-1340-7437</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라루비로 93 루비타워 4층</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://booking.naver.com/booking/12/bizes/815141</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>300</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>684</v>
+      </c>
+      <c r="R51" t="n">
+        <v>984</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>1059514904</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1059514904</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>터닝포인트짐</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>ksmturning@naver.com</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>tpgym7777@nate.com</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0507-1340-0803</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 중봉대로 594 6층 601호</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://turningpointgym.kr/</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>4</v>
+      </c>
+      <c r="R52" t="n">
+        <v>5</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>1679398325</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1679398325</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>굿무브 근골격운동센터 가정점</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>goodmove_xercise@naver.com</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0507-1336-4506</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 염곡로464번길 15 쓰리엠타워 2층 211호</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/goodmove_xercise</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>91</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>95</v>
+      </c>
+      <c r="R53" t="n">
+        <v>186</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>1371079347</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1371079347</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>커넥트바디 재활&amp;PT 청라점</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>connect-body@naver.com</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0507-1380-8515</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 보석로12번안길 35 1층</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/connect-body/223458723996</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>157</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>451</v>
+      </c>
+      <c r="R54" t="n">
+        <v>608</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>1346258755</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1346258755</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>체중감량연구소</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>udt59-91@naver.com</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0507-1431-6880</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 봉오재3로94번길 11 2층 207호</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/udt59-91</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>44</v>
+      </c>
+      <c r="R55" t="n">
+        <v>70</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>1744532291</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1744532291</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>사이언스핏 PT필라 청라점</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>sciencefit@naver.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>0507-1487-2044</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 중봉대로612번길 10-8 반안프라자 401호, 402호, 403호</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/science_fit__</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>105</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>753</v>
+      </c>
+      <c r="R56" t="n">
+        <v>858</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>1329193780</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1329193780</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>핏트레인 PT 청라</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>fittrain_@naver.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0507-1363-5598</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라한내로72번길 7-31 205호, 206호</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/fittrain_</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>49</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>86</v>
+      </c>
+      <c r="R57" t="n">
+        <v>135</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>1976065832</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1976065832</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>캐스캐이드 PT 청라점</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>cascadept@naver.com</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>0507-1311-2169</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라루비로134번길 18 1층</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://casecadept.homebuilder.co.kr</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>86</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>196</v>
+      </c>
+      <c r="R58" t="n">
+        <v>282</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>1173494121</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1173494121</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>슬릭부스트 루원시티점</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>sleekboost__lu1@naver.com</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>0507-1390-4983</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 새오개로111번안길 26 3층</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sleekboost_lu1/</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>311</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>234</v>
+      </c>
+      <c r="R59" t="n">
+        <v>545</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>1634343801</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1634343801</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>청라PT&amp;몸짱스쿨</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>kura7792@naver.com</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>0507-1343-9683</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 중봉대로586번길 9-11 매그놀리아오피스텔 3층 몸짱스쿨</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/kura7792</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>110</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>219</v>
+      </c>
+      <c r="R60" t="n">
+        <v>329</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>37547267</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37547267</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>좋은습관 PT STUDIO 청라</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>goodhabit_ch@naver.com</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>0507-1435-9902</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라한내로72번길 7-15 센트럴시티 2층 청라PT 좋은습관</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/goodhabit_ch</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>546</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>259</v>
+      </c>
+      <c r="R61" t="n">
+        <v>805</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>1404702049</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1404702049</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>마스터 와이짐 PT 청라점</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>master_y_gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라커낼로288번길 10 더스페이스타워 305호</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/master__y_gym</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>356</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>493</v>
+      </c>
+      <c r="R62" t="n">
+        <v>849</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>1200262369</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1200262369</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>청라PT 바른몸피트니스 2호점</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>barunmom_fitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>0507-1413-7437</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 중봉대로612번길 10-22 604, 605호</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>https://booking.naver.com/booking/12/bizes/1418130</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>213</v>
+      </c>
+      <c r="R63" t="n">
+        <v>291</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>2032271782</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2032271782</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>루원짐 PT 루원시티점</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>luwongym@naver.com</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청중로478번길 24 3층</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/luwongym</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>110</v>
+      </c>
+      <c r="R64" t="n">
+        <v>187</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>1538350747</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1538350747</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>웰무브 근골격운동센터 청라점</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>wellmove_ex@naver.com</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>0507-1423-9397</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라라임로 71 8층 808호, 809호 웰무브 근골격운동센터</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/wellmove_1</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>144</v>
+      </c>
+      <c r="R65" t="n">
+        <v>195</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>1594642239</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1594642239</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>클래식짐청라PT</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>classicgym-@naver.com</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>0507-1350-6909</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라한내로161번길 1 2층</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>2</v>
+      </c>
+      <c r="R66" t="n">
+        <v>29</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>2057021183</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2057021183</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>찐바디핏</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>din32@naver.com</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>0507-1377-4737</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 크리스탈로 78 엘림존 301호</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/din32</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>146</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>442</v>
+      </c>
+      <c r="R67" t="n">
+        <v>588</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>1039953052</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1039953052</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>서짐</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>seo_gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>0507-1388-1528</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라커낼로319번길 13 1층</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/seo_gym</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>69</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>3</v>
+      </c>
+      <c r="R68" t="n">
+        <v>72</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>1456524184</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1456524184</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>인바디짐 청라</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>khn9724@naver.com</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>032-563-8787</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라에메랄드로102번길 8-22</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/clement1123</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>8</v>
+      </c>
+      <c r="R69" t="n">
+        <v>35</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>33890634</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/33890634</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>하루50분 PT필라테스 청라4호점</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>rladnwjd802@naver.com</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0507-1423-7258</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라에메랄드로 78 4층 405호</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/rladnwjd802</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>128</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>122</v>
+      </c>
+      <c r="R70" t="n">
+        <v>250</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>2038838362</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2038838362</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>리커버리짐 가정점</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>rcv0715@naver.com</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>0507-1393-0213</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 봉오재3로110번길 7 504호</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/rcv0715</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>94</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>103</v>
+      </c>
+      <c r="R71" t="n">
+        <v>197</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>1133026207</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1133026207</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>조스짐 2호점</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>bonanza0917@naver.com</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0507-1417-9682</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 가정로 437 301B동 109호 조스짐</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/bonanza0917</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>150</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>125</v>
+      </c>
+      <c r="R72" t="n">
+        <v>275</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>1391522406</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1391522406</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>하루50분 PT필라테스 청라점</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>rladnwjd802@naver.com</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0507-1311-9363</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라라임로122번길 16-1 1층 101호</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/rladnwjd802</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>248</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>245</v>
+      </c>
+      <c r="R73" t="n">
+        <v>493</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>1947556374</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1947556374</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>젠틀레이디짐 PT&amp;필라테스</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>gentlelady_gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>0507-1384-8303</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라커낼로288번길 26 상가동 103동 324호</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/gentlelady_gym</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>532</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>616</v>
+      </c>
+      <c r="R74" t="n">
+        <v>1148</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>1188954884</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1188954884</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>강자존 리햅 1대1 PT샵 루원시티점</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>tjdwnsldlek@naver.com</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>0507-1365-0715</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 봉오재3로 116 3층 306호 강자존 리햅 1대1 PT샵 루원시티점</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/tjdwnsldlek/224143719751</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>94</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>69</v>
+      </c>
+      <c r="R75" t="n">
+        <v>163</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>2001611714</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2001611714</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>테오짐 PT 청라점</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>teogym@naver.com</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>0507-1373-7578</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라커낼로 280 청라골든프라자 5층 505호</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gymteogym</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>169</v>
+      </c>
+      <c r="R76" t="n">
+        <v>208</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>1814118302</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1814118302</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/청라_헬스장.xlsx
+++ b/naver-place-crawler/results_health/청라_헬스장.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로 99 지젤엠 A동 4층</t>
+          <t>인천 서구 청라에메랄드로 99 지젤엠 A동 4층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4piz5</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -646,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -675,7 +679,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로72번길 23 701호, 702호</t>
+          <t>인천 서구 청라한내로72번길 23 701호, 702호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -700,10 +704,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4orqz</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -740,7 +748,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -769,7 +777,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 서구 중봉대로586번길 15 청연프라자 10층</t>
+          <t>인천 서구 중봉대로586번길 15 청연프라자 10층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -779,7 +787,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -794,13 +802,17 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc46ox</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -834,7 +846,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -863,7 +875,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 85 C동 지하1층 101호</t>
+          <t>인천 서구 청라라임로 85 C동 지하1층 101호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -888,10 +900,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wffw3vu</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -903,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q5" t="n">
         <v>927</v>
       </c>
       <c r="R5" t="n">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -928,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1026,56 +1042,56 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>청라PT 바른몸피트니스 2호점</t>
+          <t>AMG피트니스 석남점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>barunmom_fitness@naver.com</t>
+          <t>amg5565@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1413-7437</t>
+          <t>032-572-6800</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천 서구 중봉대로612번길 10-22 604, 605호</t>
+          <t>인천 서구 길주로 79 성한캐슬 11층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/12/bizes/1418130</t>
+          <t>https://blog.naver.com/amg5565</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1085,7 +1101,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w0qh1pb</t>
+          <t>https://talk.naver.com/ct/wcfgp2</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1099,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>76</v>
+        <v>501</v>
       </c>
       <c r="Q7" t="n">
-        <v>213</v>
+        <v>613</v>
       </c>
       <c r="R7" t="n">
-        <v>289</v>
+        <v>1114</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1114,17 +1130,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2032271782</t>
+          <t>1409341657</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2032271782</t>
+          <t>https://m.place.naver.com/place/1409341657</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1152,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>청라PT 바른몸피트니스 1호점</t>
+          <t>청라PT 바른몸피트니스 2호점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1147,18 +1163,18 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1340-7437</t>
+          <t>0507-1413-7437</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천 서구 청라루비로 93 루비타워 4층</t>
+          <t>인천 서구 중봉대로612번길 10-22 604, 605호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/12/bizes/815141</t>
+          <t>https://booking.naver.com/booking/12/bizes/1418130</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1173,7 +1189,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1183,7 +1199,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w469g7</t>
+          <t>https://talk.naver.com/ct/w0qh1pb</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1197,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>300</v>
+        <v>76</v>
       </c>
       <c r="Q8" t="n">
-        <v>686</v>
+        <v>213</v>
       </c>
       <c r="R8" t="n">
-        <v>986</v>
+        <v>289</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1212,17 +1228,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1059514904</t>
+          <t>2032271782</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1059514904</t>
+          <t>https://m.place.naver.com/place/2032271782</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1234,44 +1250,44 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>웰무브 근골격운동센터 청라점</t>
+          <t>청라PT 바른몸피트니스 1호점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>wellmove_ex@naver.com</t>
+          <t>barunmom_fitness@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1423-9397</t>
+          <t>0507-1340-7437</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천 서구 청라라임로 71 8층 808호, 809호 웰무브 근골격운동센터</t>
+          <t>인천 서구 청라루비로 93 루비타워 4층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/wellmove_1</t>
+          <t>https://booking.naver.com/booking/12/bizes/815141</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1281,7 +1297,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5w2i3</t>
+          <t>https://talk.naver.com/ct/w469g7</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1295,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>51</v>
+        <v>300</v>
       </c>
       <c r="Q9" t="n">
-        <v>144</v>
+        <v>687</v>
       </c>
       <c r="R9" t="n">
-        <v>195</v>
+        <v>987</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1310,17 +1326,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1594642239</t>
+          <t>1059514904</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1594642239</t>
+          <t>https://m.place.naver.com/place/1059514904</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1332,29 +1348,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>강자존 리햅 1대1 PT샵 루원시티점</t>
+          <t>웰무브 근골격운동센터 청라점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>tjdwnsldlek@naver.com</t>
+          <t>wellmove_ex@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1365-0715</t>
+          <t>0507-1423-9397</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천 서구 봉오재3로 116 3층 306호 강자존 리햅 1대1 PT샵 루원시티점</t>
+          <t>인천 서구 청라라임로 71 8층 808호, 809호 웰무브 근골격운동센터</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/tjdwnsldlek/224143719751</t>
+          <t>https://www.instagram.com/wellmove_1</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1369,7 +1385,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1379,7 +1395,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wwi3sps</t>
+          <t>https://talk.naver.com/ct/w5w2i3</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1389,17 +1405,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>95</v>
+        <v>52</v>
       </c>
       <c r="Q10" t="n">
-        <v>69</v>
+        <v>144</v>
       </c>
       <c r="R10" t="n">
-        <v>164</v>
+        <v>196</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1408,115 +1424,311 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2001611714</t>
+          <t>1594642239</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2001611714</t>
+          <t>https://m.place.naver.com/place/1594642239</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>키필라테스 청라점</t>
+          <t>강자존 리햅 1대1 PT샵 루원시티점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>keypilates@naver.com</t>
+          <t>tjdwnsldlek@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1555-7745</t>
+          <t>0507-1365-0715</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
+          <t>인천 서구 봉오재3로 116 3층 306호 강자존 리햅 1대1 PT샵 루원시티점</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/tjdwnsldlek/224143719751</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wwi3sps</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>95</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>69</v>
+      </c>
+      <c r="R11" t="n">
+        <v>164</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>2001611714</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2001611714</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>좋은습관 PT STUDIO 청라</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>goodhabit_ch@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1435-9902</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>인천 서구 청라한내로72번길 7-15 센트럴시티 2층 청라PT 좋은습관</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/goodhabit_ch</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w46ocb</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>546</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>259</v>
+      </c>
+      <c r="R12" t="n">
+        <v>805</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1404702049</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1404702049</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>키필라테스 청라점</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>keypilates@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1555-7745</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
           <t>인천 서구 청라커낼로288번길 10 4층 408호</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>https://www.instagram.com/keypilates.kr</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
         <is>
           <t>https://talk.naver.com/ct/wyozl7z</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
         <v>15</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q13" t="n">
         <v>19</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R13" t="n">
         <v>34</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
         <is>
           <t>2074412271</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/2074412271</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/청라_헬스장.xlsx
+++ b/naver-place-crawler/results_health/청라_헬스장.xlsx
@@ -417,16 +417,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="49" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>청라스포츠센터 헬스 PT</t>
+          <t>크롬 트레이닝 스튜디오</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>uzwuzw@naver.com</t>
+          <t>chrome2026@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1300-4100</t>
+          <t>0507-1314-3439</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천 서구 청라에메랄드로 99 지젤엠 A동 4층</t>
+          <t>인천광역시 서구 봉오재3로94번길 11 mk타워 3층 308, 309호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/csc_training_center</t>
+          <t>https://blog.naver.com/chrome2026</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,19 +601,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4piz5</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -625,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2827</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>1229</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
-        <v>4056</v>
+        <v>3</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1213983093</t>
+          <t>2002611415</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1213983093</t>
+          <t>https://m.place.naver.com/place/2002611415</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -662,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>머슬피플 피트니스 헬스 PT 청라</t>
+          <t>청라스포츠센터 헬스 PT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>kdkkdk8399@naver.com</t>
+          <t>uzwuzw@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1339-0000</t>
+          <t>0507-1300-4100</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천 서구 청라한내로72번길 23 701호, 702호</t>
+          <t>인천광역시 서구 청라에메랄드로 99 지젤엠 A동 4층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/kdkkdk8399</t>
+          <t>https://www.instagram.com/csc_training_center</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -699,19 +695,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4orqz</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -723,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>370</v>
+        <v>2827</v>
       </c>
       <c r="Q3" t="n">
-        <v>1161</v>
+        <v>1229</v>
       </c>
       <c r="R3" t="n">
-        <v>1531</v>
+        <v>4056</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1197174862</t>
+          <t>1213983093</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1197174862</t>
+          <t>https://m.place.naver.com/place/1213983093</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -755,34 +747,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>바디소나타 헬스 PT 청라</t>
+          <t>센스짐 석남점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>body_sonata@naver.com</t>
+          <t>sensegym_jjy@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0507-1404-7217</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천 서구 중봉대로586번길 15 청연프라자 10층</t>
+          <t>인천광역시 서구 가정로 308 석남프라자 B1층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://2080ttt.wixsite.com/bodysonata</t>
+          <t>https://litt.ly/sensegym_jjy</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -797,22 +785,18 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wc46ox</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -821,13 +805,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1578</v>
+        <v>1293</v>
       </c>
       <c r="Q4" t="n">
-        <v>1573</v>
+        <v>617</v>
       </c>
       <c r="R4" t="n">
-        <v>3151</v>
+        <v>1910</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,12 +820,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>38782467</t>
+          <t>1507969525</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38782467</t>
+          <t>https://m.place.naver.com/place/1507969525</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -858,29 +842,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>청라헬스장 킹짐7호점 24시 헬스 PT</t>
+          <t>에이에이헬스 PT&amp;필라테스재활 청라점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>kinggym7@naver.com</t>
+          <t>somin7369@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1410-9579</t>
+          <t>0507-1340-8864</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천 서구 청라라임로 85 C동 지하1층 101호</t>
+          <t>인천광역시 서구 청라커낼로260번길 27 스타벅스 청라 한신점 오른편 지하1층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/kinggym7</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -890,24 +874,20 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wffw3vu</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -915,17 +895,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>219</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>927</v>
+        <v>195</v>
       </c>
       <c r="R5" t="n">
-        <v>1146</v>
+        <v>195</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,12 +914,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2068038054</t>
+          <t>2076358875</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2068038054</t>
+          <t>https://m.place.naver.com/place/2076358875</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -951,64 +931,60 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>터닝포인트짐 헬스 PT&amp;필라테스 청라점</t>
+          <t>피지컬뷰티짐 신현점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>tpgym6@naver.com</t>
+          <t>physicalbeauty@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1340-9221</t>
+          <t>0507-1302-0654</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천 서구 중봉대로 594 비전프라자 10층</t>
+          <t>인천광역시 서구 가정로 369 4층 401호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.tpgymcheongna.kr</t>
+          <t>https://www.youtube.com/c/피지컬뷰티</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4o7qi</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1017,13 +993,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>417</v>
+        <v>375</v>
       </c>
       <c r="Q6" t="n">
-        <v>3424</v>
+        <v>1103</v>
       </c>
       <c r="R6" t="n">
-        <v>3841</v>
+        <v>1478</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,12 +1008,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>37450365</t>
+          <t>1383014310</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37450365</t>
+          <t>https://m.place.naver.com/place/1383014310</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1054,29 +1030,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AMG피트니스 석남점</t>
+          <t>엔알 휘트니스 경서점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>amg5565@naver.com</t>
+          <t>hayth1212@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>032-572-6800</t>
+          <t>0507-1367-7749</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천 서구 길주로 79 성한캐슬 11층</t>
+          <t>인천광역시 서구 도요지로 24 2층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/amg5565</t>
+          <t>https://blog.naver.com/hayth1212</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1096,14 +1072,10 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wcfgp2</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1115,13 +1087,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>501</v>
+        <v>177</v>
       </c>
       <c r="Q7" t="n">
-        <v>613</v>
+        <v>295</v>
       </c>
       <c r="R7" t="n">
-        <v>1114</v>
+        <v>472</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,12 +1102,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1409341657</t>
+          <t>37373516</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1409341657</t>
+          <t>https://m.place.naver.com/place/37373516</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1147,34 +1119,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>청라PT 바른몸피트니스 2호점</t>
+          <t>여성전용 아이리스짐&amp;필라테스</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>barunmom_fitness@naver.com</t>
+          <t>irisgym@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1413-7437</t>
+          <t>0507-1356-0413</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천 서구 중봉대로612번길 10-22 604, 605호</t>
+          <t>인천광역시 서구 청라에메랄드로102번길 8-26 301호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/12/bizes/1418130</t>
+          <t>https://smartstore.naver.com/</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1184,7 +1156,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1194,14 +1166,10 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w0qh1pb</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1213,13 +1181,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>76</v>
+        <v>175</v>
       </c>
       <c r="Q8" t="n">
-        <v>213</v>
+        <v>321</v>
       </c>
       <c r="R8" t="n">
-        <v>289</v>
+        <v>496</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,12 +1196,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2032271782</t>
+          <t>1553359701</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2032271782</t>
+          <t>https://m.place.naver.com/place/1553359701</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1245,64 +1213,60 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>청라PT 바른몸피트니스 1호점</t>
+          <t>고다짐 청라점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>barunmom_fitness@naver.com</t>
+          <t>cjdfk2402@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1340-7437</t>
+          <t>032-565-5466</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천 서구 청라루비로 93 루비타워 4층</t>
+          <t>인천광역시 서구 청라에메랄드로 134 상가동 지1층 비103호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/12/bizes/815141</t>
+          <t>https://www.godagym.com</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w469g7</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1311,13 +1275,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>300</v>
+        <v>132</v>
       </c>
       <c r="Q9" t="n">
-        <v>687</v>
+        <v>455</v>
       </c>
       <c r="R9" t="n">
-        <v>987</v>
+        <v>587</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,12 +1290,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1059514904</t>
+          <t>1295044192</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1059514904</t>
+          <t>https://m.place.naver.com/place/1295044192</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1348,29 +1312,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>웰무브 근골격운동센터 청라점</t>
+          <t>청라 피트니스비에이 PT&amp;헬스</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>wellmove_ex@naver.com</t>
+          <t>fitnessba@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1423-9397</t>
+          <t>0507-1359-0563</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천 서구 청라라임로 71 8층 808호, 809호 웰무브 근골격운동센터</t>
+          <t>인천광역시 서구 푸른로16번길 15 1층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/wellmove_1</t>
+          <t>https://blog.naver.com/fitnessba</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1385,19 +1349,15 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5w2i3</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1409,13 +1369,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="Q10" t="n">
-        <v>144</v>
+        <v>61</v>
       </c>
       <c r="R10" t="n">
-        <v>196</v>
+        <v>90</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1424,12 +1384,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1594642239</t>
+          <t>1922697320</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1594642239</t>
+          <t>https://m.place.naver.com/place/1922697320</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1446,29 +1406,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>강자존 리햅 1대1 PT샵 루원시티점</t>
+          <t>레인헬스PT 서구청점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>tjdwnsldlek@naver.com</t>
+          <t>sonyeopps@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1365-0715</t>
+          <t>0507-1487-0787</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천 서구 봉오재3로 116 3층 306호 강자존 리햅 1대1 PT샵 루원시티점</t>
+          <t>인천광역시 서구 탁옥로 37 2층 201호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/tjdwnsldlek/224143719751</t>
+          <t>https://blog.naver.com/sonyeopps</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1488,14 +1448,10 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wwi3sps</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1503,17 +1459,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>95</v>
+        <v>125</v>
       </c>
       <c r="Q11" t="n">
-        <v>69</v>
+        <v>167</v>
       </c>
       <c r="R11" t="n">
-        <v>164</v>
+        <v>292</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1522,12 +1478,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2001611714</t>
+          <t>1799609656</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2001611714</t>
+          <t>https://m.place.naver.com/place/1799609656</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1539,34 +1495,34 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>좋은습관 PT STUDIO 청라</t>
+          <t>핏박스 PT&amp;그룹PT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>goodhabit_ch@naver.com</t>
+          <t>master_ssim@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1435-9902</t>
+          <t>0507-1370-8932</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>인천 서구 청라한내로72번길 7-15 센트럴시티 2층 청라PT 좋은습관</t>
+          <t>인천광역시 서구 중봉대로 588 9층 핏박스PT</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/goodhabit_ch</t>
+          <t>https://blog.naver.com/master_ssim</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1586,14 +1542,10 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w46ocb</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>X</t>
@@ -1605,13 +1557,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>546</v>
+        <v>120</v>
       </c>
       <c r="Q12" t="n">
-        <v>259</v>
+        <v>456</v>
       </c>
       <c r="R12" t="n">
-        <v>805</v>
+        <v>576</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1620,12 +1572,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1404702049</t>
+          <t>1839479269</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1404702049</t>
+          <t>https://m.place.naver.com/place/1839479269</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1637,34 +1589,34 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>키필라테스 청라점</t>
+          <t>전칠성의 히어로짐 헬스 PT 그룹PT 청라점</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>keypilates@naver.com</t>
+          <t>whitemurder@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1555-7745</t>
+          <t>0507-1323-9682</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>인천 서구 청라커낼로288번길 10 4층 408호</t>
+          <t>인천광역시 서구 청라커낼로260번길 7-11 퍼스트타워 7층 전칠성의 히어로짐 청라점</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/keypilates.kr</t>
+          <t>https://blog.naver.com/whitemurder/224211279556</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1679,19 +1631,15 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wyozl7z</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>X</t>
@@ -1703,13 +1651,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>15</v>
+        <v>173</v>
       </c>
       <c r="Q13" t="n">
-        <v>19</v>
+        <v>495</v>
       </c>
       <c r="R13" t="n">
-        <v>34</v>
+        <v>668</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1718,15 +1666,5997 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2074412271</t>
+          <t>1613152191</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2074412271</t>
+          <t>https://m.place.naver.com/place/1613152191</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>바디소나타 헬스 PT 청라</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>body_sonata@naver.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0507-1404-7217</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 중봉대로586번길 15 청연프라자 10층</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://2080ttt.wixsite.com/bodysonata</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc46ox</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>1578</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1574</v>
+      </c>
+      <c r="R14" t="n">
+        <v>3152</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>38782467</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38782467</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>제로짐 재활운동연구소 청라</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>zero_gym00@naver.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0507-1493-3498</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 중봉대로586번길 9-19 2층 청라 제로짐</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5v4ws</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>84</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>415</v>
+      </c>
+      <c r="R15" t="n">
+        <v>499</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1735402390</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1735402390</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>터닝포인트짐 헬스 PT&amp;필라테스 청라점</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>tpgym6@naver.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0507-1340-9221</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 중봉대로 594 비전프라자 10층</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://www.tpgymcheongna.kr</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4o7qi</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>417</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3424</v>
+      </c>
+      <c r="R16" t="n">
+        <v>3841</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>37450365</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37450365</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>머슬피플 피트니스 헬스 PT 청라</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>kdkkdk8399@naver.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0507-1339-0000</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라한내로72번길 23 701호, 702호</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4orqz</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>370</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1161</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1531</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1197174862</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1197174862</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>크로스핏 A4U</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>kwlcl707@naver.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0507-1352-7329</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 담지로86번길 16-36 1층 A4U CROSSFIT</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w2d935e</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>88</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>101</v>
+      </c>
+      <c r="R18" t="n">
+        <v>189</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>1104364395</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1104364395</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>스밀로짐 헬스 PT 청라</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>smilogym@naver.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0507-1360-1516</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라커낼로260번길 7-19 6층 스밀로짐</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w426al</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>87</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>46</v>
+      </c>
+      <c r="R19" t="n">
+        <v>133</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>1711058369</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1711058369</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>F45 청라</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>f45cheongna@naver.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라루비로 76 2층 F45 청라</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>30</v>
+      </c>
+      <c r="R20" t="n">
+        <v>32</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>2038283950</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2038283950</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>행복 휘트니스</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>maengdrive_@naver.com</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0507-1376-3581</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 새오개로54번길 15-1 3층</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/_shinseok_/</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>6</v>
+      </c>
+      <c r="R21" t="n">
+        <v>12</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>1455766468</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1455766468</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>펌퍼스짐 헬스&amp;PT 청라</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>pumper_gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0507-1476-9054</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라한내로 110 파이낸스센터 6층</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5i8k8</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>256</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>255</v>
+      </c>
+      <c r="R22" t="n">
+        <v>511</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>1828279952</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1828279952</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>휘트니트센터</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>rnltls5612@naver.com</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라커낼로 232</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>5</v>
+      </c>
+      <c r="R23" t="n">
+        <v>10</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>85758557</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/85758557</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>와이짐휘트니스</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>moonseok84@naver.com</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0507-1364-9607</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라커낼로260번길 11 4층 401호</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4nifn</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>94</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>166</v>
+      </c>
+      <c r="R24" t="n">
+        <v>260</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>1999952799</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1999952799</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>크로스핏 피포피 가정점</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>bow14674@naver.com</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0507-1345-3994</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 새오개로111번안길 19-1 지하 1층</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/bow14674</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>84</v>
+      </c>
+      <c r="R25" t="n">
+        <v>139</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>1971300109</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1971300109</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>엘티시앤짐</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0507-1431-5227</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라한내로 96 8층 802호</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2</v>
+      </c>
+      <c r="R26" t="n">
+        <v>2</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>2002395008</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2002395008</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>세인트피트니스 청라점 PT&amp;헬스</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>soccerkkw2@naver.com</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0507-1354-4659</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라라임로 71 진영메디피아 9층 905호</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4ru2d</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>948</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>916</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1864</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>1577621981</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1577621981</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>포텐휘트니스 헬스&amp;PT 루원시티점 24시</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>eohgdt4618@naver.com</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0507-1454-0823</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 봉오재3로 111 정석빌딩 4, 5층</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/eohgdt4618</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>201</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>739</v>
+      </c>
+      <c r="R28" t="n">
+        <v>940</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>1191364163</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1191364163</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>팬텀짐 루원시티점</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>phantomgym_lu1@naver.com</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0507-1331-0050</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 새오개로111번안길 19-1 유성프라자 401, 402, 403호</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w40il5</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>757</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>457</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1214</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>1088258551</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1088258551</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>트리니티 피트니스 헬스 PT 청라</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>trinity_fit@naver.com</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 크리스탈로 84 청라 레이크가든 빌딩 5층</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4ajba</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>919</v>
+      </c>
+      <c r="R30" t="n">
+        <v>999</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>1044334882</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1044334882</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>록 피트니스 R.O.K 헬스&amp;PT 가정점</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>rok03903@naver.com</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 염곡로464번길 23 엔시티타워 7층</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w2fqcva</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>723</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1173</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1896</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>1475425565</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1475425565</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>청년피티 청라점</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>cnpt3455@naver.com</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0507-1434-3455</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 중봉대로 610 3층</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://cnptoffical.qshop.ai/</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>433</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>235</v>
+      </c>
+      <c r="R32" t="n">
+        <v>668</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>1293398871</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1293398871</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>하운드짐</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>houndgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0507-1313-9986</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 솔빛로28번길 12 리마프라자 2층</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/houndgym</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>99</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>149</v>
+      </c>
+      <c r="R33" t="n">
+        <v>248</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>1606787218</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1606787218</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>아놀드홍짐 청라점</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>hanki1213@naver.com</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>032-567-8296</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 중봉대로 587 홈플러스6층</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/hanki1213</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>281</v>
+      </c>
+      <c r="R34" t="n">
+        <v>284</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>37288445</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37288445</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>프리짐 청라점</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>freegym24@naver.com</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0507-1397-6779</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라한내로72번길 17 3층 307~312호</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/freegym24</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>103</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>103</v>
+      </c>
+      <c r="R35" t="n">
+        <v>206</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>1241238840</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1241238840</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>바른피티샵</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>kyh880903@naver.com</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0507-1354-3897</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 중봉대로612번길 10-22 2층</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>142</v>
+      </c>
+      <c r="R36" t="n">
+        <v>242</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>1845302007</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1845302007</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>터닝포인트짐 헬스&amp;PT 신현점</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>turning1210@naver.com</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0507-1368-9220</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 가정로 375 5층 터닝포인트짐 신현점</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/turning1210</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>956</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>1939</v>
+      </c>
+      <c r="R37" t="n">
+        <v>2895</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>37452550</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37452550</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>청라헬스장 킹짐7호점 24시 헬스 PT</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>kinggym7@naver.com</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0507-1410-9579</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라라임로 85 C동 지하1층 101호</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/kinggym7</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>219</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>927</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1146</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>2068038054</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2068038054</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>올나잇 피트니스 가정점 헬스&amp;PT</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>all_night_b@naver.com</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0507-1475-6636</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 가정로 451 벨라미센텀시티2차 13층 1320호</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5uwcy</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>1742</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>536</v>
+      </c>
+      <c r="R39" t="n">
+        <v>2278</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>1898172914</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1898172914</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>크로스핏 굿데이</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>hooksuksuk@naver.com</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0507-1470-7606</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 승학로 223 지하1층</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/crossfit_goodday</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>7</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>1117551454</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1117551454</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>피지컬뷰티짐 청라점 PT &amp; 헬스</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>physicalbeauty@naver.com</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0507-1358-0655</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라커낼로 270 2층 피지컬뷰티짐 청라점</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/c/피지컬뷰티</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>88</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>511</v>
+      </c>
+      <c r="R41" t="n">
+        <v>599</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>1693588410</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1693588410</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>카우짐24시 서구청역점</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>coco951215@naver.com</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0507-1376-7926</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 탁옥로51번길 11 702호, 703호, 704호</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://link.inpock.co.kr/cowgymseogu</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>1020</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>324</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1344</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>1106839652</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1106839652</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>어라운드 헬스&amp;PT 청라</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>aroundgym_1@naver.com</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0507-1327-9593</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 중봉대로586번길 9-4 3층 307호 어라운드 헬스&amp;PT</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/aroundgym_1</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>393</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>286</v>
+      </c>
+      <c r="R43" t="n">
+        <v>679</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>1698654705</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1698654705</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>크로스핏 청라</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>kwlcl707@naver.com</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0507-1337-5001</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 보석로 4 1층</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>http://cafe.naver.com/crossfitcheongna</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>603</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>68</v>
+      </c>
+      <c r="R44" t="n">
+        <v>671</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>1600815804</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1600815804</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>청라웰카운티스포츠센터</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>newstation@naver.com</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라에메랄드로 156</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
+        <v>27</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>1074312806</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1074312806</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>해시피트니스 청라점</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>hashfit@naver.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0507-1492-3101</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라한내로 96 하엘에스페이스12층</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hashfit_ness/</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>533</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>735</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1268</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>1799409304</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1799409304</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>캐스캐이드 PT 청라점</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>cascadept@naver.com</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0507-1311-2169</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라루비로134번길 18 1층</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://casecadept.homebuilder.co.kr</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>86</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>196</v>
+      </c>
+      <c r="R47" t="n">
+        <v>282</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>1173494121</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1173494121</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>웰무브 근골격운동센터 청라점</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>wellmove_ex@naver.com</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0507-1423-9397</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라라임로 71 8층 808호, 809호 웰무브 근골격운동센터</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/wellmove_1</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>52</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>144</v>
+      </c>
+      <c r="R48" t="n">
+        <v>196</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>1594642239</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1594642239</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>하루50분 PT필라테스 가정5호점</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>rladnwjd802@naver.com</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0507-1309-6293</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 염곡로498번안길 18 이규프라자 3층</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>http://www.haru50.com</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>2</v>
+      </c>
+      <c r="R49" t="n">
+        <v>2</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>2084849885</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2084849885</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>체중감량연구소</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>udt59-91@naver.com</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0507-1431-6880</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 봉오재3로94번길 11 2층 207호</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/udt59-91</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>44</v>
+      </c>
+      <c r="R50" t="n">
+        <v>70</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>1744532291</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1744532291</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>청라PT 바른몸피트니스 2호점</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>barunmom_fitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0507-1413-7437</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 중봉대로612번길 10-22 604, 605호</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://booking.naver.com/booking/12/bizes/1418130</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>76</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>213</v>
+      </c>
+      <c r="R51" t="n">
+        <v>289</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>2032271782</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2032271782</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>터닝포인트짐</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>ksmturning@naver.com</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>tpgym7777@nate.com</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0507-1340-0803</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 중봉대로 594 6층 601호</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://turningpointgym.kr/</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>4</v>
+      </c>
+      <c r="R52" t="n">
+        <v>5</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>1679398325</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1679398325</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>클래식짐청라PT</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>classicgym-@naver.com</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0507-1350-6909</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라한내로161번길 1 2층</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>2</v>
+      </c>
+      <c r="R53" t="n">
+        <v>29</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>2057021183</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2057021183</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>청라PT&amp;몸짱스쿨</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>kura7792@naver.com</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0507-1343-9683</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 중봉대로586번길 9-11 매그놀리아오피스텔 3층 몸짱스쿨</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4ik3l</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>110</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>219</v>
+      </c>
+      <c r="R54" t="n">
+        <v>329</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>37547267</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37547267</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>젠틀레이디짐 PT&amp;필라테스</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>gentlelady_gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0507-1384-8303</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라커낼로288번길 26 상가동 103동 324호</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5urqn</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>532</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>618</v>
+      </c>
+      <c r="R55" t="n">
+        <v>1150</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>1188954884</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1188954884</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>테오짐 PT 청라점</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>teogym@naver.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>0507-1373-7578</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라커낼로 280 청라골든프라자 5층 505호</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gymteogym</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>169</v>
+      </c>
+      <c r="R56" t="n">
+        <v>208</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>1814118302</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1814118302</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>엑스짐 신현점</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>xfitness3@naver.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0507-1402-2033</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 가정로 419 . 4층 401호, 402호(신현동)</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wx6k73b</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>120</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>430</v>
+      </c>
+      <c r="R57" t="n">
+        <v>550</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>1413141073</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1413141073</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>루원짐 PT 루원시티점</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>luwongym@naver.com</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청중로478번길 24 3층</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wdci3r2</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>110</v>
+      </c>
+      <c r="R58" t="n">
+        <v>187</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>1538350747</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1538350747</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>인바디짐 청라</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>khn9724@naver.com</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>032-563-8787</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라에메랄드로102번길 8-22</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/clement1123</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>8</v>
+      </c>
+      <c r="R59" t="n">
+        <v>35</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>33890634</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/33890634</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>서짐</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>seo_gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>0507-1388-1528</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라커낼로319번길 13 1층</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/seo_gym</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>69</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>3</v>
+      </c>
+      <c r="R60" t="n">
+        <v>72</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>1456524184</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1456524184</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>사이언스핏 PT필라 청라점</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>sciencefit@naver.com</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>0507-1487-2044</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 중봉대로612번길 10-8 반안프라자 401호, 402호, 403호</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4agng</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>105</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>757</v>
+      </c>
+      <c r="R61" t="n">
+        <v>862</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>1329193780</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1329193780</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>마스터 와이짐 PT 청라점</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>master_y_gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라커낼로288번길 10 더스페이스타워 305호</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/master__y_gym</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>356</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>494</v>
+      </c>
+      <c r="R62" t="n">
+        <v>850</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>1200262369</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1200262369</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>슬릭부스트 루원시티점</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>sleekboost__lu1@naver.com</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>0507-1390-4983</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 새오개로111번안길 26 3층</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sleekboost_lu1/</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>312</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>234</v>
+      </c>
+      <c r="R63" t="n">
+        <v>546</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>1634343801</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1634343801</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>커넥트바디 재활&amp;PT 청라점</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>connect-body@naver.com</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0507-1380-8515</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 보석로12번안길 35 1층</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/connect-body/223458723996</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>157</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>451</v>
+      </c>
+      <c r="R64" t="n">
+        <v>608</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>1346258755</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1346258755</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>굿무브 근골격운동센터 가정점</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>goodmove_xercise@naver.com</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>0507-1336-4506</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 염곡로464번길 15 쓰리엠타워 2층 211호</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4aztz</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>91</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>95</v>
+      </c>
+      <c r="R65" t="n">
+        <v>186</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>1371079347</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1371079347</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>조스짐 2호점</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>chosgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>0507-1417-9682</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 가정로 437 301B동 109호 조스짐</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5tkir</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>150</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>125</v>
+      </c>
+      <c r="R66" t="n">
+        <v>275</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>1391522406</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1391522406</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>리커버리짐 가정점</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>rcv0715@naver.com</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>0507-1393-0213</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 봉오재3로110번길 7 504호</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/rcv0715</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>94</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>103</v>
+      </c>
+      <c r="R67" t="n">
+        <v>197</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>1133026207</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1133026207</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>핏트레인 PT 청라</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>fittrain_@naver.com</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>0507-1363-5598</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라한내로72번길 7-31 205호, 206호</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/fittrain_</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>49</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>86</v>
+      </c>
+      <c r="R68" t="n">
+        <v>135</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>1976065832</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1976065832</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>하루50분 PT필라테스 청라4호점</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>rladnwjd802@naver.com</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>0507-1423-7258</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라에메랄드로 78 4층 405호</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/rladnwjd802</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>128</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>122</v>
+      </c>
+      <c r="R69" t="n">
+        <v>250</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>2038838362</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2038838362</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>하루50분 PT필라테스 청라점</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>rladnwjd802@naver.com</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0507-1311-9363</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라라임로122번길 16-1 1층 101호</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/rladnwjd802</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>248</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>245</v>
+      </c>
+      <c r="R70" t="n">
+        <v>493</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>1947556374</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1947556374</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>청라PT 바른몸피트니스 1호점</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>barunmom_fitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>0507-1340-7437</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라루비로 93 루비타워 4층</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>https://booking.naver.com/booking/12/bizes/815141</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>300</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>693</v>
+      </c>
+      <c r="R71" t="n">
+        <v>993</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>1059514904</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1059514904</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>엘핏 청라점</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>lemongym-cn@naver.com</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0507-1428-5104</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 옥빛로13번길 3 1층 엘핏</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w6amn5j</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>89</v>
+      </c>
+      <c r="R72" t="n">
+        <v>154</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>1196898702</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1196898702</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>강자존 리햅 1대1 PT샵 루원시티점</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>tjdwnsldlek@naver.com</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0507-1365-0715</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 봉오재3로 116 3층 306호 강자존 리햅 1대1 PT샵 루원시티점</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wwi3sps</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>95</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>69</v>
+      </c>
+      <c r="R73" t="n">
+        <v>164</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>2001611714</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2001611714</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>찐바디핏</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>din32@naver.com</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>0507-1377-4737</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 크리스탈로 78 엘림존 301호</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/din32</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>146</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>442</v>
+      </c>
+      <c r="R74" t="n">
+        <v>588</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>1039953052</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1039953052</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>좋은습관 PT STUDIO 청라</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>goodhabit_ch@naver.com</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>0507-1435-9902</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라한내로72번길 7-15 센트럴시티 2층 청라PT 좋은습관</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/goodhabit_ch</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>546</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>259</v>
+      </c>
+      <c r="R75" t="n">
+        <v>805</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>1404702049</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1404702049</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>마이짐 PT 청라점</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>better__life@naver.com</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>0507-1378-3868</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 중봉대로612번길 10-20 6층 마이짐</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mygym_pt_official?igsh=dGMxNWw2eG40MWtx</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>57</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>396</v>
+      </c>
+      <c r="R76" t="n">
+        <v>453</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>1099553298</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1099553298</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>

--- a/naver-place-crawler/results_health/청라_헬스장.xlsx
+++ b/naver-place-crawler/results_health/청라_헬스장.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="49" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>전칠성의 히어로짐 헬스 PT 그룹PT 청라점</t>
+          <t>와이짐휘트니스</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>whitemurder@naver.com</t>
+          <t>moonseok84@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1323-9682</t>
+          <t>0507-1364-9607</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천 서구 청라커낼로260번길 7-11 퍼스트타워 7층 전칠성의 히어로짐 청라점</t>
+          <t>인천광역시 서구 청라커낼로260번길 11 4층 401호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/whitemurder/224211279556</t>
+          <t>https://blog.naver.com/moonseok84</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -606,14 +606,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4vnk5</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -625,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>174</v>
+        <v>94</v>
       </c>
       <c r="Q2" t="n">
-        <v>495</v>
+        <v>166</v>
       </c>
       <c r="R2" t="n">
-        <v>669</v>
+        <v>260</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1613152191</t>
+          <t>1999952799</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1613152191</t>
+          <t>https://m.place.naver.com/place/1999952799</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -662,44 +658,40 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>청라스포츠센터 헬스 PT</t>
+          <t>휘트니트센터</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>uzwuzw@naver.com</t>
+          <t>rnltls5612@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0507-1300-4100</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로 99 지젤엠 A동 4층</t>
+          <t>인천광역시 서구 청라커낼로 232</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/csc_training_center</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -715,17 +707,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2829</v>
+        <v>5</v>
       </c>
       <c r="Q3" t="n">
-        <v>1229</v>
+        <v>5</v>
       </c>
       <c r="R3" t="n">
-        <v>4058</v>
+        <v>10</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,17 +726,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1213983093</t>
+          <t>85758557</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1213983093</t>
+          <t>https://m.place.naver.com/place/85758557</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -756,34 +748,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>청라헬스장 킹짐7호점 24시 헬스 PT</t>
+          <t>여성전용 아이리스짐&amp;필라테스</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>kinggym7@naver.com</t>
+          <t>irisgym@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1410-9579</t>
+          <t>0507-1356-0413</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 85 C동 지하1층 101호</t>
+          <t>인천광역시 서구 청라에메랄드로102번길 8-26 301호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/kinggym7</t>
+          <t>https://smartstore.naver.com/</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -793,7 +785,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -813,13 +805,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>219</v>
+        <v>176</v>
       </c>
       <c r="Q4" t="n">
-        <v>927</v>
+        <v>321</v>
       </c>
       <c r="R4" t="n">
-        <v>1146</v>
+        <v>497</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -828,17 +820,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2068038054</t>
+          <t>1553359701</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2068038054</t>
+          <t>https://m.place.naver.com/place/1553359701</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -850,29 +842,25 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>머슬피플 피트니스 헬스 PT 청라</t>
+          <t>청라웰카운티스포츠센터</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>kdkkdk8399@naver.com</t>
+          <t>newstation@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0507-1339-0000</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로72번길 23 701호, 702호</t>
+          <t>인천광역시 서구 청라에메랄드로 156</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/kdkkdk8399</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -882,12 +870,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -903,17 +891,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>370</v>
+        <v>27</v>
       </c>
       <c r="Q5" t="n">
-        <v>1162</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1532</v>
+        <v>27</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -922,51 +910,51 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1197174862</t>
+          <t>1074312806</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1197174862</t>
+          <t>https://m.place.naver.com/place/1074312806</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>바디소나타 헬스 PT 청라</t>
+          <t>프리짐 청라점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>body_sonata@naver.com</t>
+          <t>freegym24@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1404-7217</t>
+          <t>0507-1397-6779</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 서구 중봉대로586번길 15 청연프라자 10층</t>
+          <t>인천광역시 서구 청라한내로72번길 17 3층 307~312호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://2080ttt.wixsite.com/bodysonata</t>
+          <t>https://blog.naver.com/freegym24</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1001,13 +989,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1579</v>
+        <v>103</v>
       </c>
       <c r="Q6" t="n">
-        <v>1577</v>
+        <v>103</v>
       </c>
       <c r="R6" t="n">
-        <v>3156</v>
+        <v>206</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1016,81 +1004,77 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>38782467</t>
+          <t>1241238840</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38782467</t>
+          <t>https://m.place.naver.com/place/1241238840</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>터닝포인트짐 헬스 PT&amp;필라테스 청라점</t>
+          <t>팬텀짐 루원시티점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>tpgym6@naver.com</t>
+          <t>phantomgym_lu1@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1340-9221</t>
+          <t>0507-1331-0050</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천 서구 중봉대로 594 비전프라자 10층</t>
+          <t>인천광역시 서구 새오개로111번안길 19-1 유성프라자 401, 402, 403호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.tpgymcheongna.kr</t>
+          <t>https://blog.naver.com/phantomgym_lu1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4o7qi</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1099,13 +1083,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>417</v>
+        <v>757</v>
       </c>
       <c r="Q7" t="n">
-        <v>3429</v>
+        <v>457</v>
       </c>
       <c r="R7" t="n">
-        <v>3846</v>
+        <v>1214</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1114,78 +1098,74 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>37450365</t>
+          <t>1088258551</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37450365</t>
+          <t>https://m.place.naver.com/place/1088258551</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>청라PT 바른몸피트니스 2호점</t>
+          <t>포텐휘트니스 헬스&amp;PT 루원시티점 24시</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>barunmom_fitness@naver.com</t>
+          <t>eohgdt4618@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1413-7437</t>
+          <t>0507-1454-0823</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천 서구 중봉대로612번길 10-22 604, 605호</t>
+          <t>인천광역시 서구 봉오재3로 111 정석빌딩 4, 5층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/12/bizes/1418130</t>
+          <t>https://blog.naver.com/eohgdt4618</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w0qh1pb</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1197,13 +1177,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>76</v>
+        <v>201</v>
       </c>
       <c r="Q8" t="n">
-        <v>213</v>
+        <v>739</v>
       </c>
       <c r="R8" t="n">
-        <v>289</v>
+        <v>940</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1212,78 +1192,74 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2032271782</t>
+          <t>1191364163</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2032271782</t>
+          <t>https://m.place.naver.com/place/1191364163</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>청라PT 바른몸피트니스 1호점</t>
+          <t>해시피트니스 청라점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>barunmom_fitness@naver.com</t>
+          <t>hashfit@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1340-7437</t>
+          <t>0507-1492-3101</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천 서구 청라루비로 93 루비타워 4층</t>
+          <t>인천광역시 서구 청라한내로 96 하엘에스페이스12층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/12/bizes/815141</t>
+          <t>https://www.instagram.com/hashfit_ness/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w469g7</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1295,13 +1271,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>300</v>
+        <v>534</v>
       </c>
       <c r="Q9" t="n">
-        <v>697</v>
+        <v>735</v>
       </c>
       <c r="R9" t="n">
-        <v>997</v>
+        <v>1269</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1310,51 +1286,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1059514904</t>
+          <t>1799409304</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1059514904</t>
+          <t>https://m.place.naver.com/place/1799409304</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>웰무브 근골격운동센터 청라점</t>
+          <t>크로스핏 굿데이</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>wellmove_ex@naver.com</t>
+          <t>hooksuksuk@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1423-9397</t>
+          <t>0507-1470-7606</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천 서구 청라라임로 71 8층 808호, 809호 웰무브 근골격운동센터</t>
+          <t>인천광역시 서구 승학로 223 지하1층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/wellmove_1</t>
+          <t>https://www.instagram.com/crossfit_goodday</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1374,14 +1350,10 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5w2i3</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1393,13 +1365,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>144</v>
+        <v>7</v>
       </c>
       <c r="R10" t="n">
-        <v>196</v>
+        <v>7</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1408,51 +1380,51 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1594642239</t>
+          <t>1117551454</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1594642239</t>
+          <t>https://m.place.naver.com/place/1117551454</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>강자존 리햅 1대1 PT샵 루원시티점</t>
+          <t>엔알 휘트니스 경서점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>tjdwnsldlek@naver.com</t>
+          <t>hayth1212@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1365-0715</t>
+          <t>0507-1367-7749</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천 서구 봉오재3로 116 3층 306호 강자존 리햅 1대1 PT샵 루원시티점</t>
+          <t>인천광역시 서구 도요지로 24 2층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/tjdwnsldlek/224143719751</t>
+          <t>https://blog.naver.com/hayth1212</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1472,14 +1444,10 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wwi3sps</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1487,17 +1455,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>95</v>
+        <v>177</v>
       </c>
       <c r="Q11" t="n">
-        <v>69</v>
+        <v>295</v>
       </c>
       <c r="R11" t="n">
-        <v>164</v>
+        <v>472</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1506,51 +1474,51 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2001611714</t>
+          <t>37373516</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2001611714</t>
+          <t>https://m.place.naver.com/place/37373516</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>키필라테스 청라점</t>
+          <t>바른피티샵</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>keypilates@naver.com</t>
+          <t>kyh880903@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1555-7745</t>
+          <t>0507-1354-3897</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>인천 서구 청라커낼로288번길 10 4층 408호</t>
+          <t>인천광역시 서구 중봉대로612번길 10-22 2층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/keypilates.kr</t>
+          <t>https://blog.naver.com/kyh880903</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1565,19 +1533,15 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wyozl7z</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>X</t>
@@ -1589,13 +1553,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="Q12" t="n">
-        <v>19</v>
+        <v>143</v>
       </c>
       <c r="R12" t="n">
-        <v>34</v>
+        <v>243</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1604,17 +1568,6009 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2074412271</t>
+          <t>1845302007</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2074412271</t>
+          <t>https://m.place.naver.com/place/1845302007</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>크롬 트레이닝 스튜디오</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>chrome2026@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1314-3439</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 봉오재3로94번길 11 mk타워 3층 308, 309호</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/chrome2026</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3</v>
+      </c>
+      <c r="R13" t="n">
+        <v>3</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>2002611415</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2002611415</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>제로짐 재활운동연구소 청라</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>zero_gym00@naver.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0507-1493-3498</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 중봉대로586번길 9-19 2층 청라 제로짐</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/zero_gym00</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>84</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>415</v>
+      </c>
+      <c r="R14" t="n">
+        <v>499</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>1735402390</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1735402390</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>스밀로짐 헬스 PT 청라</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>smilogym@naver.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0507-1360-1516</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라커낼로260번길 7-19 6층 스밀로짐</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/smilogym</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>87</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>46</v>
+      </c>
+      <c r="R15" t="n">
+        <v>133</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1711058369</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1711058369</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>청라헬스장 킹짐7호점 24시 헬스 PT</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>kinggym7@naver.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0507-1410-9579</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라라임로 85 C동 지하1층 101호</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/kinggym7</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>218</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>927</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1145</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>2068038054</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2068038054</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>올나잇 피트니스 가정점 헬스&amp;PT</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>rdx329@naver.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0507-1475-6636</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 가정로 451 벨라미센텀시티2차 13층 1320호</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/all.night_3</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>1744</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>536</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2280</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1898172914</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1898172914</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>터닝포인트짐 헬스&amp;PT 신현점</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>turning1210@naver.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0507-1368-9220</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 가정로 375 5층 터닝포인트짐 신현점</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/turning1210</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>956</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1944</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2900</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>37452550</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37452550</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>전칠성의 히어로짐 헬스 PT 그룹PT 청라점</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>whitemurder@naver.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0507-1323-9682</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라커낼로260번길 7-11 퍼스트타워 7층 전칠성의 히어로짐 청라점</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/whitemurder/224211279556</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>174</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>495</v>
+      </c>
+      <c r="R19" t="n">
+        <v>669</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>1613152191</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1613152191</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>행복 휘트니스</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>maengdrive_@naver.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0507-1376-3581</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 새오개로54번길 15-1 3층</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/_shinseok_/</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>6</v>
+      </c>
+      <c r="R20" t="n">
+        <v>12</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1455766468</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1455766468</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>터닝포인트짐 헬스 PT&amp;필라테스 청라점</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>tpgym6@naver.com</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0507-1340-9221</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 중봉대로 594 비전프라자 10층</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://www.tpgymcheongna.kr</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>417</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3429</v>
+      </c>
+      <c r="R21" t="n">
+        <v>3846</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>37450365</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37450365</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>고다짐 청라점</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>cjdfk2402@naver.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>032-565-5466</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라에메랄드로 134 상가동 지1층 비103호</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://www.godagym.com</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>132</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>455</v>
+      </c>
+      <c r="R22" t="n">
+        <v>587</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>1295044192</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1295044192</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>피지컬뷰티짐 신현점</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>physicalbeauty@naver.com</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0507-1302-0654</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 가정로 369 4층 401호</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/c/피지컬뷰티</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>377</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1104</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1481</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>1383014310</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1383014310</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>트리니티 피트니스 헬스 PT 청라</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>trinity_fit@naver.com</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 크리스탈로 84 청라 레이크가든 빌딩 5층</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/trinity_fit/</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>919</v>
+      </c>
+      <c r="R24" t="n">
+        <v>999</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>1044334882</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1044334882</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>에이에이헬스 PT&amp;필라테스재활 청라점</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>somin7369@naver.com</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0507-1340-8864</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라커낼로260번길 27 스타벅스 청라 한신점 오른편 지하1층</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>195</v>
+      </c>
+      <c r="R25" t="n">
+        <v>195</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>2076358875</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2076358875</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>어라운드 헬스&amp;PT 청라</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>aroundgym_1@naver.com</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0507-1327-9593</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 중봉대로586번길 9-4 3층 307호 어라운드 헬스&amp;PT</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/aroundgym_1</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>393</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>286</v>
+      </c>
+      <c r="R26" t="n">
+        <v>679</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>1698654705</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1698654705</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>청라 피트니스비에이 PT&amp;헬스</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>fitnessba@naver.com</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0507-1359-0563</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 푸른로16번길 15 1층</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/fitnessba</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>61</v>
+      </c>
+      <c r="R27" t="n">
+        <v>90</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>1922697320</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1922697320</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>크로스핏 피포피 가정점</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>bow14674@naver.com</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0507-1345-3994</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 새오개로111번안길 19-1 지하 1층</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/bow14674</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>84</v>
+      </c>
+      <c r="R28" t="n">
+        <v>139</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>1971300109</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1971300109</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>피지컬뷰티짐 청라점 PT &amp; 헬스</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>physicalbeauty@naver.com</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0507-1358-0655</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라커낼로 270 2층 피지컬뷰티짐 청라점</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/c/피지컬뷰티</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>88</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>511</v>
+      </c>
+      <c r="R29" t="n">
+        <v>599</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>1693588410</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1693588410</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>록 피트니스 R.O.K 헬스&amp;PT 가정점</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>rok03903@naver.com</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 염곡로464번길 23 엔시티타워 7층</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/rok03903</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>727</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1173</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1900</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>1475425565</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1475425565</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>핏박스 PT&amp;그룹PT</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>master_ssim@naver.com</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0507-1370-8932</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 중봉대로 588 9층 핏박스PT</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/master_ssim</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>120</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>456</v>
+      </c>
+      <c r="R31" t="n">
+        <v>576</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>1839479269</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1839479269</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>레인헬스PT 서구청점</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>sonyeopps@naver.com</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0507-1487-0787</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 탁옥로 37 2층 201호</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/sonyeopps</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>125</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>168</v>
+      </c>
+      <c r="R32" t="n">
+        <v>293</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>1799609656</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1799609656</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>펌퍼스짐 헬스&amp;PT 청라</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>pumper_gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0507-1476-9054</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라한내로 110 파이낸스센터 6층</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/pumpers_gym?igsh=MXJueDAwamF5cWpheQ%3D%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>256</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>258</v>
+      </c>
+      <c r="R33" t="n">
+        <v>514</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>1828279952</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1828279952</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>크로스핏 청라</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>kwlcl707@naver.com</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0507-1337-5001</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 보석로 4 1층</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>http://cafe.naver.com/crossfitcheongna</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>603</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>68</v>
+      </c>
+      <c r="R34" t="n">
+        <v>671</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>1600815804</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1600815804</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>크로스핏 A4U</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>kwlcl707@naver.com</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0507-1352-7329</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 담지로86번길 16-36 1층 A4U CROSSFIT</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/crossfit_a4u</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>88</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>101</v>
+      </c>
+      <c r="R35" t="n">
+        <v>189</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>1104364395</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1104364395</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>센스짐 석남점</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>sensegym_jjy@naver.com</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 가정로 308 석남프라자 B1층</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://litt.ly/sensegym_jjy</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>1296</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>618</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1914</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>1507969525</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1507969525</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>엘티시앤짐</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0507-1431-5227</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라한내로 96 8층 802호</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>2</v>
+      </c>
+      <c r="R37" t="n">
+        <v>2</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>2002395008</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2002395008</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>카우짐24시 서구청역점</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>coco951215@naver.com</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0507-1376-7926</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 탁옥로51번길 11 702호, 703호, 704호</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://link.inpock.co.kr/cowgymseogu</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>1020</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>324</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1344</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>1106839652</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1106839652</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>아놀드홍짐 청라점</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>hanki1213@naver.com</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>032-567-8296</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 중봉대로 587 홈플러스6층</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/hanki1213</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>281</v>
+      </c>
+      <c r="R39" t="n">
+        <v>284</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>37288445</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37288445</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>하운드짐</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>houndgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0507-1313-9986</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 솔빛로28번길 12 리마프라자 2층</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/houndgym</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>102</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>149</v>
+      </c>
+      <c r="R40" t="n">
+        <v>251</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>1606787218</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1606787218</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>F45 청라</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>f45cheongna@naver.com</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라루비로 76 2층 F45 청라</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/f45cheongna</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>29</v>
+      </c>
+      <c r="R41" t="n">
+        <v>31</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>2038283950</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2038283950</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>청년피티 청라점</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>cnpt3455@naver.com</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0507-1434-3455</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 중봉대로 610 3층</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://cnptoffical.qshop.ai/</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>433</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>236</v>
+      </c>
+      <c r="R42" t="n">
+        <v>669</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>1293398871</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1293398871</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>머슬피플 피트니스 헬스 PT 청라</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>kdkkdk8399@naver.com</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0507-1339-0000</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라한내로72번길 23 701호, 702호</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/kdkkdk8399</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>370</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>1162</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1532</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>1197174862</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1197174862</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>바디소나타 헬스 PT 청라</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>body_sonata@naver.com</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0507-1404-7217</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 중봉대로586번길 15 청연프라자 10층</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://2080ttt.wixsite.com/bodysonata</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>1580</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>1579</v>
+      </c>
+      <c r="R44" t="n">
+        <v>3159</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>38782467</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38782467</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>세인트피트니스 청라점 PT&amp;헬스</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>soccerkkw2@naver.com</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0507-1354-4659</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라라임로 71 진영메디피아 9층 905호</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/soccerkkw2</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>948</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>916</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1864</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>1577621981</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1577621981</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>청라스포츠센터 헬스 PT</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>uzwuzw@naver.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0507-1300-4100</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라에메랄드로 99 지젤엠 A동 4층</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/csc_training_center</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>2832</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>1229</v>
+      </c>
+      <c r="R46" t="n">
+        <v>4061</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>1213983093</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1213983093</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>테오짐 PT 청라점</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>teogym@naver.com</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0507-1373-7578</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라커낼로 280 청라골든프라자 5층 505호</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gymteogym</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>170</v>
+      </c>
+      <c r="R47" t="n">
+        <v>209</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>1814118302</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1814118302</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>웰무브 근골격운동센터 청라점</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>wellmove_ex@naver.com</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0507-1423-9397</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라라임로 71 8층 808호, 809호 웰무브 근골격운동센터</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/wellmove_1</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>52</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>144</v>
+      </c>
+      <c r="R48" t="n">
+        <v>196</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>1594642239</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1594642239</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>터닝포인트짐</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>ksmturning@naver.com</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>tpgym7777@nate.com</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0507-1340-0803</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 중봉대로 594 6층 601호</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://turningpointgym.kr/</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>4</v>
+      </c>
+      <c r="R49" t="n">
+        <v>5</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>1679398325</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1679398325</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>핏트레인 PT 청라</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>fittrain_@naver.com</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0507-1363-5598</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라한내로72번길 7-31 205호, 206호</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/fittrain_</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>49</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>86</v>
+      </c>
+      <c r="R50" t="n">
+        <v>135</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>1976065832</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1976065832</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>하루50분 PT필라테스 청라점</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>rladnwjd802@naver.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0507-1311-9363</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라라임로122번길 16-1 1층 101호</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/rladnwjd802</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>248</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>245</v>
+      </c>
+      <c r="R51" t="n">
+        <v>493</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>1947556374</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1947556374</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>서짐</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>seo_gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0507-1388-1528</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라커낼로319번길 13 1층</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/seo_gym</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>69</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>3</v>
+      </c>
+      <c r="R52" t="n">
+        <v>72</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>1456524184</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1456524184</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>리커버리짐 가정점</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>rcv0715@naver.com</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0507-1393-0213</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 봉오재3로110번길 7 504호</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/rcv0715</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>94</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>103</v>
+      </c>
+      <c r="R53" t="n">
+        <v>197</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>1133026207</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1133026207</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>좋은습관 PT STUDIO 청라</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>goodhabit_ch@naver.com</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0507-1435-9902</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라한내로72번길 7-15 센트럴시티 2층 청라PT 좋은습관</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/goodhabit_ch</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>546</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>259</v>
+      </c>
+      <c r="R54" t="n">
+        <v>805</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>1404702049</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1404702049</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>강자존 리햅 1대1 PT샵 루원시티점</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>tjdwnsldlek@naver.com</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0507-1365-0715</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 봉오재3로 116 3층 306호 강자존 리햅 1대1 PT샵 루원시티점</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/tjdwnsldlek/224143719751</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>95</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>69</v>
+      </c>
+      <c r="R55" t="n">
+        <v>164</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>2001611714</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2001611714</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>청라PT&amp;몸짱스쿨</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>kura7792@naver.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>0507-1343-9683</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 중봉대로586번길 9-11 매그놀리아오피스텔 3층 몸짱스쿨</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/kura7792</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>110</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>219</v>
+      </c>
+      <c r="R56" t="n">
+        <v>329</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>37547267</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37547267</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>청라PT 바른몸피트니스 1호점</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>barunmom_fitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0507-1340-7437</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라루비로 93 루비타워 4층</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://booking.naver.com/booking/12/bizes/815141</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>300</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>697</v>
+      </c>
+      <c r="R57" t="n">
+        <v>997</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>1059514904</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1059514904</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>슬릭부스트 루원시티점</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>sleekboost__lu1@naver.com</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>0507-1390-4983</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 새오개로111번안길 26 3층</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sleekboost_lu1/</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>312</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>234</v>
+      </c>
+      <c r="R58" t="n">
+        <v>546</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>1634343801</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1634343801</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>루원짐 PT 루원시티점</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>luwongym@naver.com</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청중로478번길 24 3층</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/luwongym</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>110</v>
+      </c>
+      <c r="R59" t="n">
+        <v>187</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>1538350747</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1538350747</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>조스짐 2호점</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>bonanza0917@naver.com</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>0507-1417-9682</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 가정로 437 301B동 109호 조스짐</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/bonanza0917</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>150</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>125</v>
+      </c>
+      <c r="R60" t="n">
+        <v>275</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>1391522406</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1391522406</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>마스터 와이짐 PT 청라점</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>master_y_gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라커낼로288번길 10 더스페이스타워 305호</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/master__y_gym</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>356</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>494</v>
+      </c>
+      <c r="R61" t="n">
+        <v>850</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>1200262369</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1200262369</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>하루50분 PT필라테스 가정5호점</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>rladnwjd802@naver.com</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0507-1309-6293</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 염곡로498번안길 18 이규프라자 3층</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>http://www.haru50.com</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>3</v>
+      </c>
+      <c r="R62" t="n">
+        <v>3</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>2084849885</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2084849885</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>캐스캐이드 PT 청라점</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>cascadept@naver.com</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>0507-1311-2169</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라루비로134번길 18 1층</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>https://casecadept.homebuilder.co.kr</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>86</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>197</v>
+      </c>
+      <c r="R63" t="n">
+        <v>283</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>1173494121</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1173494121</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>찐바디핏</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>din32@naver.com</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0507-1377-4737</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 크리스탈로 78 엘림존 301호</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/din32</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>146</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>443</v>
+      </c>
+      <c r="R64" t="n">
+        <v>589</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>1039953052</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1039953052</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>클래식짐청라PT</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>classicgym-@naver.com</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>0507-1350-6909</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라한내로161번길 1 2층</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>2</v>
+      </c>
+      <c r="R65" t="n">
+        <v>29</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>2057021183</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2057021183</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>엘핏 청라점</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>lemongym-cn@naver.com</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>0507-1428-5104</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 옥빛로13번길 3 1층 엘핏</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/lemongym-cn</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>89</v>
+      </c>
+      <c r="R66" t="n">
+        <v>154</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>1196898702</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1196898702</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>젠틀레이디짐 PT&amp;필라테스</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>gentlelady_gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>0507-1384-8303</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라커낼로288번길 26 상가동 103동 324호</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/gentlelady_gym</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>532</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>620</v>
+      </c>
+      <c r="R67" t="n">
+        <v>1152</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>1188954884</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1188954884</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>굿무브 근골격운동센터 가정점</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>goodmove_xercise@naver.com</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>0507-1336-4506</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 염곡로464번길 15 쓰리엠타워 2층 211호</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/goodmove_xercise</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>91</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>95</v>
+      </c>
+      <c r="R68" t="n">
+        <v>186</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>1371079347</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1371079347</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>하루50분 PT필라테스 청라4호점</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>rladnwjd802@naver.com</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>0507-1423-7258</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라에메랄드로 78 4층 405호</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/rladnwjd802</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>129</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>123</v>
+      </c>
+      <c r="R69" t="n">
+        <v>252</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>2038838362</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2038838362</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>체중감량연구소</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>udt59-91@naver.com</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0507-1431-6880</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 봉오재3로94번길 11 2층 207호</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/udt59-91</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>44</v>
+      </c>
+      <c r="R70" t="n">
+        <v>70</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>1744532291</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1744532291</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>엑스짐 신현점</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>xgym01@naver.com</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>0507-1402-2033</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 가정로 419 . 4층 401호, 402호(신현동)</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/x_gym_can?igsh=NGxodHQ0b2FlbWFr</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>120</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>430</v>
+      </c>
+      <c r="R71" t="n">
+        <v>550</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>1413141073</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1413141073</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>마이짐 PT 청라점</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>better__life@naver.com</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0507-1378-3868</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 중봉대로612번길 10-20 6층 마이짐</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mygym_pt_official?igsh=dGMxNWw2eG40MWtx</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>57</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>396</v>
+      </c>
+      <c r="R72" t="n">
+        <v>453</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>1099553298</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1099553298</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>사이언스핏 PT필라 청라점</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>sciencefit@naver.com</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0507-1487-2044</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 중봉대로612번길 10-8 반안프라자 401호, 402호, 403호</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/science_fit__</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>105</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>761</v>
+      </c>
+      <c r="R73" t="n">
+        <v>866</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>1329193780</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1329193780</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>인바디짐 청라</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>khn9724@naver.com</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>032-563-8787</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라에메랄드로102번길 8-22</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/clement1123</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>8</v>
+      </c>
+      <c r="R74" t="n">
+        <v>35</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>33890634</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/33890634</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>청라PT 바른몸피트니스 2호점</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>barunmom_fitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>0507-1413-7437</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 중봉대로612번길 10-22 604, 605호</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>https://booking.naver.com/booking/12/bizes/1418130</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>213</v>
+      </c>
+      <c r="R75" t="n">
+        <v>288</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>2032271782</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2032271782</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>커넥트바디 재활&amp;PT 청라점</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>connect-body@naver.com</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>0507-1380-8515</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 보석로12번안길 35 1층</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/connect-body/223458723996</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>157</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>451</v>
+      </c>
+      <c r="R76" t="n">
+        <v>608</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>1346258755</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1346258755</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/청라_헬스장.xlsx
+++ b/naver-place-crawler/results_health/청라_헬스장.xlsx
@@ -417,11 +417,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -564,34 +564,30 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>전칠성의 히어로짐 헬스 PT 그룹PT 청라점</t>
+          <t>크로스핏 졸리 영종점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>whitemurder@naver.com</t>
+          <t>jollymolly_3@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0507-1323-9682</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천 서구 청라커낼로260번길 7-11 퍼스트타워 7층 전칠성의 히어로짐 청라점</t>
+          <t>인천광역시 중구 운중로 137-81 트레이닝 졸리</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/whitemurder/224211279556</t>
+          <t>https://cafe.naver.com/jollymolly</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -601,19 +597,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4vnk5</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -625,13 +617,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>175</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>495</v>
+        <v>11</v>
       </c>
       <c r="R2" t="n">
-        <v>670</v>
+        <v>11</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,17 +632,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1613152191</t>
+          <t>2059999621</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1613152191</t>
+          <t>https://m.place.naver.com/place/2059999621</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -679,7 +671,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천 서구 청라에메랄드로 99 지젤엠 A동 4층</t>
+          <t>인천광역시 서구 청라에메랄드로 99 지젤엠 A동 4층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -704,14 +696,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4piz5</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -748,7 +736,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -777,7 +765,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천 서구 청라라임로 85 C동 지하1층 101호</t>
+          <t>인천광역시 서구 청라라임로 85 C동 지하1층 101호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -802,14 +790,10 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wffw3vu</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -846,7 +830,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -875,7 +859,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천 서구 청라한내로72번길 23 701호, 702호</t>
+          <t>인천광역시 서구 청라한내로72번길 23 701호, 702호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -900,14 +884,10 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4orqz</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -944,7 +924,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -983,7 +963,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1008,7 +988,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1017,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1580</v>
+        <v>1582</v>
       </c>
       <c r="Q6" t="n">
         <v>1583</v>
       </c>
       <c r="R6" t="n">
-        <v>3163</v>
+        <v>3165</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1042,7 +1022,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1120,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1152,34 +1132,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>여성전용 아이리스짐&amp;필라테스</t>
+          <t>AMG피트니스 석남점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>irisgym@naver.com</t>
+          <t>amg5565@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1356-0413</t>
+          <t>032-572-6800</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천 서구 청라에메랄드로102번길 8-26 301호</t>
+          <t>인천 서구 길주로 79 성한캐슬 11층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://smartstore.naver.com/</t>
+          <t>https://blog.naver.com/amg5565</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1189,7 +1169,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1199,7 +1179,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4p17z</t>
+          <t>https://talk.naver.com/ct/wcfgp2</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1213,13 +1193,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>176</v>
+        <v>501</v>
       </c>
       <c r="Q8" t="n">
-        <v>321</v>
+        <v>614</v>
       </c>
       <c r="R8" t="n">
-        <v>497</v>
+        <v>1115</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,17 +1208,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1553359701</t>
+          <t>1409341657</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1553359701</t>
+          <t>https://m.place.naver.com/place/1409341657</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1316,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1414,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1512,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1610,203 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>좋은습관 PT STUDIO 청라</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>goodhabit_ch@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1435-9902</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>인천 서구 청라한내로72번길 7-15 센트럴시티 2층 청라PT 좋은습관</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/goodhabit_ch</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w46ocb</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>547</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>259</v>
+      </c>
+      <c r="R13" t="n">
+        <v>806</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1404702049</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1404702049</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>키필라테스 청라점</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>keypilates@naver.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1555-7745</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>인천 서구 청라커낼로288번길 10 4층 408호</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/keypilates.kr</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wyozl7z</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>19</v>
+      </c>
+      <c r="R14" t="n">
+        <v>34</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>2074412271</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2074412271</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/청라_헬스장.xlsx
+++ b/naver-place-crawler/results_health/청라_헬스장.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V14"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -564,30 +564,34 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>크로스핏 졸리 영종점</t>
+          <t>청라스포츠센터 헬스 PT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>jollymolly_3@naver.com</t>
+          <t>uzwuzw@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0507-1300-4100</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천광역시 중구 운중로 137-81 트레이닝 졸리</t>
+          <t>인천 서구 청라에메랄드로 99 지젤엠 A동 4층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://cafe.naver.com/jollymolly</t>
+          <t>https://www.instagram.com/csc_training_center</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -602,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4piz5</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -617,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2834</v>
       </c>
       <c r="Q2" t="n">
-        <v>11</v>
+        <v>1229</v>
       </c>
       <c r="R2" t="n">
-        <v>11</v>
+        <v>4063</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -632,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2059999621</t>
+          <t>1213983093</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2059999621</t>
+          <t>https://m.place.naver.com/place/1213983093</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -654,29 +662,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>청라스포츠센터 헬스 PT</t>
+          <t>청라헬스장 킹짐7호점 24시 헬스 PT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>uzwuzw@naver.com</t>
+          <t>kinggym7@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1300-4100</t>
+          <t>0507-1410-9579</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로 99 지젤엠 A동 4층</t>
+          <t>인천 서구 청라라임로 85 C동 지하1층 101호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/csc_training_center</t>
+          <t>https://blog.naver.com/kinggym7</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -691,15 +699,19 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wffw3vu</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -711,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2834</v>
+        <v>219</v>
       </c>
       <c r="Q3" t="n">
-        <v>1229</v>
+        <v>927</v>
       </c>
       <c r="R3" t="n">
-        <v>4063</v>
+        <v>1146</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -726,12 +738,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1213983093</t>
+          <t>2068038054</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1213983093</t>
+          <t>https://m.place.naver.com/place/2068038054</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -748,29 +760,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>청라헬스장 킹짐7호점 24시 헬스 PT</t>
+          <t>머슬피플 피트니스 헬스 PT 청라</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>kinggym7@naver.com</t>
+          <t>kdkkdk8399@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1410-9579</t>
+          <t>0507-1339-0000</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 85 C동 지하1층 101호</t>
+          <t>인천 서구 청라한내로72번길 23 701호, 702호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/kinggym7</t>
+          <t>https://blog.naver.com/kdkkdk8399</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -790,10 +802,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4orqz</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -805,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>219</v>
+        <v>370</v>
       </c>
       <c r="Q4" t="n">
-        <v>928</v>
+        <v>1163</v>
       </c>
       <c r="R4" t="n">
-        <v>1147</v>
+        <v>1533</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -820,12 +836,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2068038054</t>
+          <t>1197174862</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2068038054</t>
+          <t>https://m.place.naver.com/place/1197174862</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -837,34 +853,34 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>머슬피플 피트니스 헬스 PT 청라</t>
+          <t>바디소나타 헬스 PT 청라</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>kdkkdk8399@naver.com</t>
+          <t>body_sonata@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1339-0000</t>
+          <t>0507-1404-7217</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로72번길 23 701호, 702호</t>
+          <t>인천 서구 중봉대로586번길 15 청연프라자 10층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/kdkkdk8399</t>
+          <t>https://2080ttt.wixsite.com/bodysonata</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -884,10 +900,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc46ox</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -899,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>370</v>
+        <v>1582</v>
       </c>
       <c r="Q5" t="n">
-        <v>1163</v>
+        <v>1583</v>
       </c>
       <c r="R5" t="n">
-        <v>1533</v>
+        <v>3165</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -914,12 +934,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1197174862</t>
+          <t>38782467</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1197174862</t>
+          <t>https://m.place.naver.com/place/38782467</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -936,44 +956,44 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>바디소나타 헬스 PT 청라</t>
+          <t>터닝포인트짐 헬스 PT&amp;필라테스 청라점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>body_sonata@naver.com</t>
+          <t>tpgym6@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1404-7217</t>
+          <t>0507-1340-9221</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천 서구 중봉대로586번길 15 청연프라자 10층</t>
+          <t>인천 서구 중봉대로 594 비전프라자 10층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://2080ttt.wixsite.com/bodysonata</t>
+          <t>https://www.tpgymcheongna.kr</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -983,12 +1003,12 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wc46ox</t>
+          <t>https://talk.naver.com/ct/w4o7qi</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -997,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1582</v>
+        <v>417</v>
       </c>
       <c r="Q6" t="n">
-        <v>1583</v>
+        <v>3428</v>
       </c>
       <c r="R6" t="n">
-        <v>3165</v>
+        <v>3845</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,12 +1032,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>38782467</t>
+          <t>37450365</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38782467</t>
+          <t>https://m.place.naver.com/place/37450365</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1029,49 +1049,49 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>터닝포인트짐 헬스 PT&amp;필라테스 청라점</t>
+          <t>AMG피트니스 석남점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>tpgym6@naver.com</t>
+          <t>amg5565@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1340-9221</t>
+          <t>032-572-6800</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천 서구 중봉대로 594 비전프라자 10층</t>
+          <t>인천 서구 길주로 79 성한캐슬 11층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.tpgymcheongna.kr</t>
+          <t>https://blog.naver.com/amg5565</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1081,12 +1101,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4o7qi</t>
+          <t>https://talk.naver.com/ct/wcfgp2</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1095,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>417</v>
+        <v>501</v>
       </c>
       <c r="Q7" t="n">
-        <v>3428</v>
+        <v>614</v>
       </c>
       <c r="R7" t="n">
-        <v>3845</v>
+        <v>1115</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1110,12 +1130,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>37450365</t>
+          <t>1409341657</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37450365</t>
+          <t>https://m.place.naver.com/place/1409341657</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1127,49 +1147,49 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AMG피트니스 석남점</t>
+          <t>청라PT 바른몸피트니스 2호점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>amg5565@naver.com</t>
+          <t>barunmom_fitness@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>032-572-6800</t>
+          <t>0507-1413-7437</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천 서구 길주로 79 성한캐슬 11층</t>
+          <t>인천 서구 중봉대로612번길 10-22 604, 605호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/amg5565</t>
+          <t>https://booking.naver.com/booking/12/bizes/1418130</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1179,7 +1199,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wcfgp2</t>
+          <t>https://talk.naver.com/ct/w0qh1pb</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1193,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>501</v>
+        <v>75</v>
       </c>
       <c r="Q8" t="n">
-        <v>614</v>
+        <v>213</v>
       </c>
       <c r="R8" t="n">
-        <v>1115</v>
+        <v>288</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1208,12 +1228,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1409341657</t>
+          <t>2032271782</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1409341657</t>
+          <t>https://m.place.naver.com/place/2032271782</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1230,7 +1250,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>청라PT 바른몸피트니스 2호점</t>
+          <t>청라PT 바른몸피트니스 1호점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1241,18 +1261,18 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1413-7437</t>
+          <t>0507-1340-7437</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천 서구 중봉대로612번길 10-22 604, 605호</t>
+          <t>인천 서구 청라루비로 93 루비타워 4층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/12/bizes/1418130</t>
+          <t>https://booking.naver.com/booking/12/bizes/815141</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1267,7 +1287,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1277,7 +1297,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w0qh1pb</t>
+          <t>https://talk.naver.com/ct/w469g7</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1291,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>75</v>
+        <v>300</v>
       </c>
       <c r="Q9" t="n">
-        <v>213</v>
+        <v>667</v>
       </c>
       <c r="R9" t="n">
-        <v>288</v>
+        <v>967</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1306,12 +1326,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2032271782</t>
+          <t>1059514904</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2032271782</t>
+          <t>https://m.place.naver.com/place/1059514904</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1328,44 +1348,44 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>청라PT 바른몸피트니스 1호점</t>
+          <t>웰무브 근골격운동센터 청라점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>barunmom_fitness@naver.com</t>
+          <t>wellmove_ex@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1340-7437</t>
+          <t>0507-1423-9397</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천 서구 청라루비로 93 루비타워 4층</t>
+          <t>인천 서구 청라라임로 71 8층 808호, 809호 웰무브 근골격운동센터</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/12/bizes/815141</t>
+          <t>https://www.instagram.com/wellmove_1</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1375,7 +1395,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w469g7</t>
+          <t>https://talk.naver.com/ct/w5w2i3</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1389,13 +1409,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>300</v>
+        <v>52</v>
       </c>
       <c r="Q10" t="n">
-        <v>667</v>
+        <v>144</v>
       </c>
       <c r="R10" t="n">
-        <v>967</v>
+        <v>196</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1404,12 +1424,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1059514904</t>
+          <t>1594642239</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1059514904</t>
+          <t>https://m.place.naver.com/place/1594642239</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1426,29 +1446,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>웰무브 근골격운동센터 청라점</t>
+          <t>강자존 리햅 1대1 PT샵 루원시티점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>wellmove_ex@naver.com</t>
+          <t>tjdwnsldlek@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1423-9397</t>
+          <t>0507-1365-0715</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천 서구 청라라임로 71 8층 808호, 809호 웰무브 근골격운동센터</t>
+          <t>인천 서구 봉오재3로 116 3층 306호 강자존 리햅 1대1 PT샵 루원시티점</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/wellmove_1</t>
+          <t>https://blog.naver.com/tjdwnsldlek/224143719751</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1463,7 +1483,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1473,7 +1493,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5w2i3</t>
+          <t>https://talk.naver.com/ct/wwi3sps</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1483,17 +1503,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="Q11" t="n">
-        <v>144</v>
+        <v>69</v>
       </c>
       <c r="R11" t="n">
-        <v>196</v>
+        <v>165</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1502,12 +1522,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1594642239</t>
+          <t>2001611714</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1594642239</t>
+          <t>https://m.place.naver.com/place/2001611714</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1519,34 +1539,34 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>강자존 리햅 1대1 PT샵 루원시티점</t>
+          <t>키필라테스 청라점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>tjdwnsldlek@naver.com</t>
+          <t>keypilates@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1365-0715</t>
+          <t>1555-7745</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>인천 서구 봉오재3로 116 3층 306호 강자존 리햅 1대1 PT샵 루원시티점</t>
+          <t>인천 서구 청라커낼로288번길 10 4층 408호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/tjdwnsldlek/224143719751</t>
+          <t>https://www.instagram.com/keypilates.kr</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1561,7 +1581,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1571,7 +1591,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wwi3sps</t>
+          <t>https://talk.naver.com/ct/wyozl7z</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1581,17 +1601,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>96</v>
+        <v>15</v>
       </c>
       <c r="Q12" t="n">
-        <v>69</v>
+        <v>19</v>
       </c>
       <c r="R12" t="n">
-        <v>165</v>
+        <v>34</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1600,211 +1620,15 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2001611714</t>
+          <t>2074412271</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2001611714</t>
+          <t>https://m.place.naver.com/place/2074412271</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>좋은습관 PT STUDIO 청라</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>goodhabit_ch@naver.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0507-1435-9902</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>인천 서구 청라한내로72번길 7-15 센트럴시티 2층 청라PT 좋은습관</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/goodhabit_ch</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w46ocb</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>547</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>259</v>
-      </c>
-      <c r="R13" t="n">
-        <v>806</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>1404702049</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1404702049</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>필라테스</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>키필라테스 청라점</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>keypilates@naver.com</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>1555-7745</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>인천 서구 청라커낼로288번길 10 4층 408호</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/keypilates.kr</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wyozl7z</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>19</v>
-      </c>
-      <c r="R14" t="n">
-        <v>34</v>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>2074412271</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/2074412271</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
